--- a/data/Tabellarische_Darstellung.xlsx
+++ b/data/Tabellarische_Darstellung.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suma3525\OneDrive\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suma3525\01_TH Wildau\02_Forschung\2024_MK-PM Normen und Standards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39E80DE5-D481-4D46-99CB-EB33DBF0F63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06ACE9A9-B4E2-44DE-9836-720008B10001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3BF2A3B6-F95D-44C5-B263-B1FCB04FF02A}"/>
+    <workbookView xWindow="57480" yWindow="-870" windowWidth="29040" windowHeight="15720" xr2:uid="{3BF2A3B6-F95D-44C5-B263-B1FCB04FF02A}"/>
   </bookViews>
   <sheets>
     <sheet name="Version 1" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="551" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="184">
   <si>
     <t>ANSI/PMI 08-002-2024, The Standard for Program Management</t>
   </si>
@@ -2708,14 +2708,12 @@
         <v>123</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="G43" s="4" t="s">
         <v>60</v>
       </c>
+      <c r="G43" s="4"/>
     </row>
     <row r="44" spans="1:7" ht="38" thickBot="1">
       <c r="A44" s="2" t="s">

--- a/data/Tabellarische_Darstellung.xlsx
+++ b/data/Tabellarische_Darstellung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suma3525\01_TH Wildau\02_Forschung\2024_MK-PM Normen und Standards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06ACE9A9-B4E2-44DE-9836-720008B10001}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8CDC1E4-EB34-4B80-BDED-F90400DEE9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-870" windowWidth="29040" windowHeight="15720" xr2:uid="{3BF2A3B6-F95D-44C5-B263-B1FCB04FF02A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="550" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="186">
   <si>
     <t>ANSI/PMI 08-002-2024, The Standard for Program Management</t>
   </si>
@@ -972,6 +972,13 @@
   </si>
   <si>
     <t>V-Modell XT – Das deutsche Referenzmodell für Systementwicklungsprojekte, Version 2.4 (2024)</t>
+  </si>
+  <si>
+    <t>Standard für
+Commercial Project Management (2020) (added / neu aufgenommen)</t>
+  </si>
+  <si>
+    <t>Projektmanagement, Projektkalkulation</t>
   </si>
 </sst>
 </file>
@@ -1031,7 +1038,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1070,11 +1077,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1089,6 +1107,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1390,8 +1411,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC19F6B0-0587-46B4-B294-E8D476710C92}" name="Tabelle2" displayName="Tabelle2" ref="A1:G92" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
-  <autoFilter ref="A1:G92" xr:uid="{DC19F6B0-0587-46B4-B294-E8D476710C92}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC19F6B0-0587-46B4-B294-E8D476710C92}" name="Tabelle2" displayName="Tabelle2" ref="A1:G93" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
+  <autoFilter ref="A1:G93" xr:uid="{DC19F6B0-0587-46B4-B294-E8D476710C92}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{1EDA15DF-55D2-40A4-885C-A06FCAF5C0D4}" name="Titel" dataDxfId="6"/>
     <tableColumn id="7" xr3:uid="{380A952E-3AB4-42D5-8EA2-4B2FC5008100}" name="Art" dataDxfId="5"/>
@@ -1722,7 +1743,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C876F68F-E5AF-4D2C-A2F8-1E598695C57F}">
-  <dimension ref="A1:G92"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="4" width="21.25" customWidth="1"/>
@@ -3817,7 +3838,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="62.5">
+    <row r="92" spans="1:7" ht="63" thickBot="1">
       <c r="A92" s="2" t="s">
         <v>183</v>
       </c>
@@ -3838,6 +3859,29 @@
       </c>
       <c r="G92" s="4" t="s">
         <v>104</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="62.5">
+      <c r="A93" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C93" s="4">
+        <v>2020</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E93" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F93" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G93" s="6" t="s">
+        <v>185</v>
       </c>
     </row>
   </sheetData>

--- a/data/Tabellarische_Darstellung.xlsx
+++ b/data/Tabellarische_Darstellung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suma3525\01_TH Wildau\02_Forschung\2024_MK-PM Normen und Standards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8CDC1E4-EB34-4B80-BDED-F90400DEE9ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C91187-CBE0-4FFE-B788-A37A37EC86E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-870" windowWidth="29040" windowHeight="15720" xr2:uid="{3BF2A3B6-F95D-44C5-B263-B1FCB04FF02A}"/>
   </bookViews>
@@ -974,11 +974,10 @@
     <t>V-Modell XT – Das deutsche Referenzmodell für Systementwicklungsprojekte, Version 2.4 (2024)</t>
   </si>
   <si>
-    <t>Standard für
-Commercial Project Management (2020) (added / neu aufgenommen)</t>
-  </si>
-  <si>
     <t>Projektmanagement, Projektkalkulation</t>
+  </si>
+  <si>
+    <t>Standard für Commercial Project Management (2020) (added / neu aufgenommen)</t>
   </si>
 </sst>
 </file>
@@ -3861,9 +3860,9 @@
         <v>104</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="62.5">
+    <row r="93" spans="1:7" ht="50">
       <c r="A93" s="6" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>108</v>
@@ -3881,7 +3880,7 @@
         <v>62</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
   </sheetData>

--- a/data/Tabellarische_Darstellung.xlsx
+++ b/data/Tabellarische_Darstellung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suma3525\01_TH Wildau\02_Forschung\2024_MK-PM Normen und Standards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9C91187-CBE0-4FFE-B788-A37A37EC86E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF87156-1252-401F-9FB6-993462F303F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="57480" yWindow="-870" windowWidth="29040" windowHeight="15720" xr2:uid="{3BF2A3B6-F95D-44C5-B263-B1FCB04FF02A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="186">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="187">
   <si>
     <t>ANSI/PMI 08-002-2024, The Standard for Program Management</t>
   </si>
@@ -978,6 +978,9 @@
   </si>
   <si>
     <t>Standard für Commercial Project Management (2020) (added / neu aufgenommen)</t>
+  </si>
+  <si>
+    <t>GPM Deutsche Gesellschaft für Projektmanagement e. V.</t>
   </si>
 </sst>
 </file>
@@ -3871,7 +3874,7 @@
         <v>2020</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>120</v>
+        <v>186</v>
       </c>
       <c r="E93" s="6" t="s">
         <v>48</v>

--- a/data/Tabellarische_Darstellung.xlsx
+++ b/data/Tabellarische_Darstellung.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suma3525\01_TH Wildau\02_Forschung\2024_MK-PM Normen und Standards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBF87156-1252-401F-9FB6-993462F303F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E94630A5-A59C-40DF-BE8F-F5F54F022008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="57480" yWindow="-870" windowWidth="29040" windowHeight="15720" xr2:uid="{3BF2A3B6-F95D-44C5-B263-B1FCB04FF02A}"/>
+    <workbookView xWindow="59400" yWindow="1605" windowWidth="26925" windowHeight="12825" xr2:uid="{3BF2A3B6-F95D-44C5-B263-B1FCB04FF02A}"/>
   </bookViews>
   <sheets>
     <sheet name="Version 1" sheetId="2" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="190">
   <si>
     <t>ANSI/PMI 08-002-2024, The Standard for Program Management</t>
   </si>
@@ -981,6 +981,15 @@
   </si>
   <si>
     <t>GPM Deutsche Gesellschaft für Projektmanagement e. V.</t>
+  </si>
+  <si>
+    <t>Sustainable Project Management ICB4 Reference Guide, Version 1.0 (2024) (added / neu aufgenommen)</t>
+  </si>
+  <si>
+    <t>Projektmanagement, Kompetenz, Nachhaltigkeit</t>
+  </si>
+  <si>
+    <t>Planning Competences ICB4 Reference Guide, Version 1.0 (2024) (added / neu aufgenommen)</t>
   </si>
 </sst>
 </file>
@@ -1413,8 +1422,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC19F6B0-0587-46B4-B294-E8D476710C92}" name="Tabelle2" displayName="Tabelle2" ref="A1:G93" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
-  <autoFilter ref="A1:G93" xr:uid="{DC19F6B0-0587-46B4-B294-E8D476710C92}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC19F6B0-0587-46B4-B294-E8D476710C92}" name="Tabelle2" displayName="Tabelle2" ref="A1:G95" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
+  <autoFilter ref="A1:G95" xr:uid="{DC19F6B0-0587-46B4-B294-E8D476710C92}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{1EDA15DF-55D2-40A4-885C-A06FCAF5C0D4}" name="Titel" dataDxfId="6"/>
     <tableColumn id="7" xr3:uid="{380A952E-3AB4-42D5-8EA2-4B2FC5008100}" name="Art" dataDxfId="5"/>
@@ -1745,15 +1754,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C876F68F-E5AF-4D2C-A2F8-1E598695C57F}">
-  <dimension ref="A1:G93"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
+  <dimension ref="A1:G95"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="4" width="21.25" customWidth="1"/>
-    <col min="5" max="6" width="15.08203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.08203125" customWidth="1"/>
+    <col min="5" max="6" width="15.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="14.5" thickBot="1">
+    <row r="1" spans="1:7" ht="15" thickBot="1">
       <c r="A1" s="1" t="s">
         <v>110</v>
       </c>
@@ -1776,7 +1785,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="75.5" thickBot="1">
+    <row r="2" spans="1:7" ht="77.25" thickBot="1">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -1799,7 +1808,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="75.5" thickBot="1">
+    <row r="3" spans="1:7" ht="77.25" thickBot="1">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
@@ -1822,7 +1831,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="75.5" thickBot="1">
+    <row r="4" spans="1:7" ht="77.25" thickBot="1">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
@@ -1845,7 +1854,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="75.5" thickBot="1">
+    <row r="5" spans="1:7" ht="77.25" thickBot="1">
       <c r="A5" s="5" t="s">
         <v>155</v>
       </c>
@@ -1868,7 +1877,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="25.5" thickBot="1">
+    <row r="6" spans="1:7" ht="26.25" thickBot="1">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
@@ -1891,7 +1900,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="38" thickBot="1">
+    <row r="7" spans="1:7" ht="39" thickBot="1">
       <c r="A7" s="5" t="s">
         <v>133</v>
       </c>
@@ -1914,7 +1923,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="38" thickBot="1">
+    <row r="8" spans="1:7" ht="39" thickBot="1">
       <c r="A8" s="2" t="s">
         <v>134</v>
       </c>
@@ -1937,7 +1946,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="40" thickBot="1">
+    <row r="9" spans="1:7" ht="40.5" thickBot="1">
       <c r="A9" s="5" t="s">
         <v>135</v>
       </c>
@@ -1960,7 +1969,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="40" thickBot="1">
+    <row r="10" spans="1:7" ht="39" thickBot="1">
       <c r="A10" s="2" t="s">
         <v>136</v>
       </c>
@@ -1983,7 +1992,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="40" thickBot="1">
+    <row r="11" spans="1:7" ht="40.5" thickBot="1">
       <c r="A11" s="5" t="s">
         <v>137</v>
       </c>
@@ -2006,7 +2015,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="40" thickBot="1">
+    <row r="12" spans="1:7" ht="40.5" thickBot="1">
       <c r="A12" s="2" t="s">
         <v>138</v>
       </c>
@@ -2029,7 +2038,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="38" thickBot="1">
+    <row r="13" spans="1:7" ht="39" thickBot="1">
       <c r="A13" s="5" t="s">
         <v>139</v>
       </c>
@@ -2052,7 +2061,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="50.5" thickBot="1">
+    <row r="14" spans="1:7" ht="51.75" thickBot="1">
       <c r="A14" s="2" t="s">
         <v>4</v>
       </c>
@@ -2075,7 +2084,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="38" thickBot="1">
+    <row r="15" spans="1:7" ht="39" thickBot="1">
       <c r="A15" s="5" t="s">
         <v>5</v>
       </c>
@@ -2098,7 +2107,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="50.5" thickBot="1">
+    <row r="16" spans="1:7" ht="51.75" thickBot="1">
       <c r="A16" s="2" t="s">
         <v>156</v>
       </c>
@@ -2121,7 +2130,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="75.5" thickBot="1">
+    <row r="17" spans="1:7" ht="77.25" thickBot="1">
       <c r="A17" s="5" t="s">
         <v>154</v>
       </c>
@@ -2144,7 +2153,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="113" thickBot="1">
+    <row r="18" spans="1:7" ht="102.75" thickBot="1">
       <c r="A18" s="2" t="s">
         <v>157</v>
       </c>
@@ -2167,7 +2176,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="63" thickBot="1">
+    <row r="19" spans="1:7" ht="64.5" thickBot="1">
       <c r="A19" s="5" t="s">
         <v>158</v>
       </c>
@@ -2190,7 +2199,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="50.5" thickBot="1">
+    <row r="20" spans="1:7" ht="51.75" thickBot="1">
       <c r="A20" s="2" t="s">
         <v>159</v>
       </c>
@@ -2213,7 +2222,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="63" thickBot="1">
+    <row r="21" spans="1:7" ht="64.5" thickBot="1">
       <c r="A21" s="5" t="s">
         <v>160</v>
       </c>
@@ -2236,7 +2245,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="50.5" thickBot="1">
+    <row r="22" spans="1:7" ht="51.75" thickBot="1">
       <c r="A22" s="2" t="s">
         <v>161</v>
       </c>
@@ -2259,7 +2268,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="63" thickBot="1">
+    <row r="23" spans="1:7" ht="64.5" thickBot="1">
       <c r="A23" s="5" t="s">
         <v>162</v>
       </c>
@@ -2282,7 +2291,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="75.5" thickBot="1">
+    <row r="24" spans="1:7" ht="77.25" thickBot="1">
       <c r="A24" s="2" t="s">
         <v>163</v>
       </c>
@@ -2305,7 +2314,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="50.5" thickBot="1">
+    <row r="25" spans="1:7" ht="51.75" thickBot="1">
       <c r="A25" s="5" t="s">
         <v>164</v>
       </c>
@@ -2328,7 +2337,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="88" thickBot="1">
+    <row r="26" spans="1:7" ht="90" thickBot="1">
       <c r="A26" s="2" t="s">
         <v>165</v>
       </c>
@@ -2351,7 +2360,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="75.5" thickBot="1">
+    <row r="27" spans="1:7" ht="77.25" thickBot="1">
       <c r="A27" s="5" t="s">
         <v>166</v>
       </c>
@@ -2374,7 +2383,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="50.5" thickBot="1">
+    <row r="28" spans="1:7" ht="51.75" thickBot="1">
       <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
@@ -2397,7 +2406,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="75.5" thickBot="1">
+    <row r="29" spans="1:7" ht="64.5" thickBot="1">
       <c r="A29" s="5" t="s">
         <v>167</v>
       </c>
@@ -2420,7 +2429,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="63" thickBot="1">
+    <row r="30" spans="1:7" ht="64.5" thickBot="1">
       <c r="A30" s="2" t="s">
         <v>168</v>
       </c>
@@ -2443,7 +2452,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="75.5" thickBot="1">
+    <row r="31" spans="1:7" ht="77.25" thickBot="1">
       <c r="A31" s="5" t="s">
         <v>169</v>
       </c>
@@ -2466,7 +2475,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="75.5" thickBot="1">
+    <row r="32" spans="1:7" ht="77.25" thickBot="1">
       <c r="A32" s="2" t="s">
         <v>170</v>
       </c>
@@ -2489,7 +2498,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="88" thickBot="1">
+    <row r="33" spans="1:7" ht="90" thickBot="1">
       <c r="A33" s="5" t="s">
         <v>171</v>
       </c>
@@ -2512,7 +2521,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="75.5" thickBot="1">
+    <row r="34" spans="1:7" ht="77.25" thickBot="1">
       <c r="A34" s="2" t="s">
         <v>172</v>
       </c>
@@ -2535,7 +2544,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="88" thickBot="1">
+    <row r="35" spans="1:7" ht="90" thickBot="1">
       <c r="A35" s="5" t="s">
         <v>173</v>
       </c>
@@ -2558,7 +2567,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="63" thickBot="1">
+    <row r="36" spans="1:7" ht="64.5" thickBot="1">
       <c r="A36" s="2" t="s">
         <v>174</v>
       </c>
@@ -2579,7 +2588,7 @@
       </c>
       <c r="G36" s="4"/>
     </row>
-    <row r="37" spans="1:7" ht="40" thickBot="1">
+    <row r="37" spans="1:7" ht="40.5" thickBot="1">
       <c r="A37" s="5" t="s">
         <v>140</v>
       </c>
@@ -2602,7 +2611,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="40" thickBot="1">
+    <row r="38" spans="1:7" ht="40.5" thickBot="1">
       <c r="A38" s="2" t="s">
         <v>141</v>
       </c>
@@ -2625,7 +2634,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="27.5" thickBot="1">
+    <row r="39" spans="1:7" ht="27.75" thickBot="1">
       <c r="A39" s="5" t="s">
         <v>142</v>
       </c>
@@ -2648,7 +2657,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="25.5" thickBot="1">
+    <row r="40" spans="1:7" ht="26.25" thickBot="1">
       <c r="A40" s="2" t="s">
         <v>7</v>
       </c>
@@ -2671,7 +2680,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="50.5" thickBot="1">
+    <row r="41" spans="1:7" ht="39" thickBot="1">
       <c r="A41" s="5" t="s">
         <v>8</v>
       </c>
@@ -2694,7 +2703,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="63" thickBot="1">
+    <row r="42" spans="1:7" ht="64.5" thickBot="1">
       <c r="A42" s="2" t="s">
         <v>9</v>
       </c>
@@ -2717,7 +2726,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="63" thickBot="1">
+    <row r="43" spans="1:7" ht="64.5" thickBot="1">
       <c r="A43" s="5" t="s">
         <v>143</v>
       </c>
@@ -2738,7 +2747,7 @@
       </c>
       <c r="G43" s="4"/>
     </row>
-    <row r="44" spans="1:7" ht="38" thickBot="1">
+    <row r="44" spans="1:7" ht="39" thickBot="1">
       <c r="A44" s="2" t="s">
         <v>144</v>
       </c>
@@ -2761,7 +2770,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="38" thickBot="1">
+    <row r="45" spans="1:7" ht="39" thickBot="1">
       <c r="A45" s="5" t="s">
         <v>10</v>
       </c>
@@ -2784,7 +2793,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="75.5" thickBot="1">
+    <row r="46" spans="1:7" ht="77.25" thickBot="1">
       <c r="A46" s="2" t="s">
         <v>175</v>
       </c>
@@ -2807,7 +2816,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="52.5" thickBot="1">
+    <row r="47" spans="1:7" ht="53.25" thickBot="1">
       <c r="A47" s="5" t="s">
         <v>145</v>
       </c>
@@ -2830,7 +2839,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="50.5" thickBot="1">
+    <row r="48" spans="1:7" ht="51.75" thickBot="1">
       <c r="A48" s="2" t="s">
         <v>146</v>
       </c>
@@ -2853,7 +2862,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="52.5" thickBot="1">
+    <row r="49" spans="1:7" ht="53.25" thickBot="1">
       <c r="A49" s="5" t="s">
         <v>147</v>
       </c>
@@ -2876,7 +2885,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="38" thickBot="1">
+    <row r="50" spans="1:7" ht="39" thickBot="1">
       <c r="A50" s="2" t="s">
         <v>11</v>
       </c>
@@ -2899,7 +2908,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="38" thickBot="1">
+    <row r="51" spans="1:7" ht="39" thickBot="1">
       <c r="A51" s="5" t="s">
         <v>12</v>
       </c>
@@ -2922,7 +2931,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="38" thickBot="1">
+    <row r="52" spans="1:7" ht="39" thickBot="1">
       <c r="A52" s="2" t="s">
         <v>13</v>
       </c>
@@ -2945,7 +2954,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="50.5" thickBot="1">
+    <row r="53" spans="1:7" ht="51.75" thickBot="1">
       <c r="A53" s="5" t="s">
         <v>14</v>
       </c>
@@ -2968,7 +2977,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="63" thickBot="1">
+    <row r="54" spans="1:7" ht="64.5" thickBot="1">
       <c r="A54" s="2" t="s">
         <v>176</v>
       </c>
@@ -2991,7 +3000,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="88" thickBot="1">
+    <row r="55" spans="1:7" ht="77.25" thickBot="1">
       <c r="A55" s="5" t="s">
         <v>177</v>
       </c>
@@ -3014,7 +3023,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="88" thickBot="1">
+    <row r="56" spans="1:7" ht="90" thickBot="1">
       <c r="A56" s="2" t="s">
         <v>178</v>
       </c>
@@ -3037,7 +3046,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="75.5" thickBot="1">
+    <row r="57" spans="1:7" ht="77.25" thickBot="1">
       <c r="A57" s="5" t="s">
         <v>179</v>
       </c>
@@ -3060,7 +3069,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="75.5" thickBot="1">
+    <row r="58" spans="1:7" ht="77.25" thickBot="1">
       <c r="A58" s="2" t="s">
         <v>180</v>
       </c>
@@ -3083,7 +3092,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="52.5" thickBot="1">
+    <row r="59" spans="1:7" ht="53.25" thickBot="1">
       <c r="A59" s="5" t="s">
         <v>148</v>
       </c>
@@ -3106,7 +3115,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="50.5" thickBot="1">
+    <row r="60" spans="1:7" ht="51.75" thickBot="1">
       <c r="A60" s="2" t="s">
         <v>15</v>
       </c>
@@ -3129,7 +3138,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="77.5" thickBot="1">
+    <row r="61" spans="1:7" ht="78.75" thickBot="1">
       <c r="A61" s="5" t="s">
         <v>149</v>
       </c>
@@ -3152,7 +3161,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="38" thickBot="1">
+    <row r="62" spans="1:7" ht="39" thickBot="1">
       <c r="A62" s="2" t="s">
         <v>16</v>
       </c>
@@ -3175,7 +3184,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="40" thickBot="1">
+    <row r="63" spans="1:7" ht="40.5" thickBot="1">
       <c r="A63" s="5" t="s">
         <v>150</v>
       </c>
@@ -3198,7 +3207,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="50.5" thickBot="1">
+    <row r="64" spans="1:7" ht="51.75" thickBot="1">
       <c r="A64" s="2" t="s">
         <v>151</v>
       </c>
@@ -3221,7 +3230,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="50.5" thickBot="1">
+    <row r="65" spans="1:7" ht="51.75" thickBot="1">
       <c r="A65" s="5" t="s">
         <v>17</v>
       </c>
@@ -3244,7 +3253,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="50.5" thickBot="1">
+    <row r="66" spans="1:7" ht="51.75" thickBot="1">
       <c r="A66" s="2" t="s">
         <v>18</v>
       </c>
@@ -3267,7 +3276,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="50.5" thickBot="1">
+    <row r="67" spans="1:7" ht="51.75" thickBot="1">
       <c r="A67" s="5" t="s">
         <v>19</v>
       </c>
@@ -3290,7 +3299,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="63" thickBot="1">
+    <row r="68" spans="1:7" ht="64.5" thickBot="1">
       <c r="A68" s="2" t="s">
         <v>20</v>
       </c>
@@ -3313,7 +3322,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="50.5" thickBot="1">
+    <row r="69" spans="1:7" ht="51.75" thickBot="1">
       <c r="A69" s="5" t="s">
         <v>21</v>
       </c>
@@ -3336,7 +3345,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="50.5" thickBot="1">
+    <row r="70" spans="1:7" ht="51.75" thickBot="1">
       <c r="A70" s="2" t="s">
         <v>22</v>
       </c>
@@ -3359,7 +3368,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="38" thickBot="1">
+    <row r="71" spans="1:7" ht="39" thickBot="1">
       <c r="A71" s="5" t="s">
         <v>23</v>
       </c>
@@ -3382,7 +3391,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="50.5" thickBot="1">
+    <row r="72" spans="1:7" ht="51.75" thickBot="1">
       <c r="A72" s="2" t="s">
         <v>24</v>
       </c>
@@ -3405,7 +3414,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="50.5" thickBot="1">
+    <row r="73" spans="1:7" ht="51.75" thickBot="1">
       <c r="A73" s="5" t="s">
         <v>25</v>
       </c>
@@ -3428,7 +3437,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="63" thickBot="1">
+    <row r="74" spans="1:7" ht="64.5" thickBot="1">
       <c r="A74" s="2" t="s">
         <v>26</v>
       </c>
@@ -3451,7 +3460,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="63" thickBot="1">
+    <row r="75" spans="1:7" ht="64.5" thickBot="1">
       <c r="A75" s="5" t="s">
         <v>27</v>
       </c>
@@ -3474,7 +3483,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="25.5" thickBot="1">
+    <row r="76" spans="1:7" ht="26.25" thickBot="1">
       <c r="A76" s="2" t="s">
         <v>28</v>
       </c>
@@ -3497,7 +3506,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="52.5" thickBot="1">
+    <row r="77" spans="1:7" ht="53.25" thickBot="1">
       <c r="A77" s="5" t="s">
         <v>152</v>
       </c>
@@ -3520,7 +3529,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="78" spans="1:7" ht="38" thickBot="1">
+    <row r="78" spans="1:7" ht="39" thickBot="1">
       <c r="A78" s="2" t="s">
         <v>29</v>
       </c>
@@ -3543,7 +3552,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="79" spans="1:7" ht="38" thickBot="1">
+    <row r="79" spans="1:7" ht="39" thickBot="1">
       <c r="A79" s="5" t="s">
         <v>30</v>
       </c>
@@ -3566,7 +3575,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="80" spans="1:7" ht="38" thickBot="1">
+    <row r="80" spans="1:7" ht="39" thickBot="1">
       <c r="A80" s="2" t="s">
         <v>31</v>
       </c>
@@ -3589,7 +3598,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="81" spans="1:7" ht="38" thickBot="1">
+    <row r="81" spans="1:7" ht="39" thickBot="1">
       <c r="A81" s="5" t="s">
         <v>32</v>
       </c>
@@ -3612,7 +3621,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="82" spans="1:7" ht="38" thickBot="1">
+    <row r="82" spans="1:7" ht="39" thickBot="1">
       <c r="A82" s="2" t="s">
         <v>33</v>
       </c>
@@ -3635,7 +3644,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="83" spans="1:7" ht="50.5" thickBot="1">
+    <row r="83" spans="1:7" ht="51.75" thickBot="1">
       <c r="A83" s="5" t="s">
         <v>34</v>
       </c>
@@ -3658,7 +3667,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="84" spans="1:7" ht="38" thickBot="1">
+    <row r="84" spans="1:7" ht="39" thickBot="1">
       <c r="A84" s="2" t="s">
         <v>35</v>
       </c>
@@ -3679,7 +3688,7 @@
       </c>
       <c r="G84" s="4"/>
     </row>
-    <row r="85" spans="1:7" ht="25.5" thickBot="1">
+    <row r="85" spans="1:7" ht="26.25" thickBot="1">
       <c r="A85" s="5" t="s">
         <v>36</v>
       </c>
@@ -3702,7 +3711,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="86" spans="1:7" ht="27.5" thickBot="1">
+    <row r="86" spans="1:7" ht="27.75" thickBot="1">
       <c r="A86" s="2" t="s">
         <v>153</v>
       </c>
@@ -3725,7 +3734,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="87" spans="1:7" ht="100.5" thickBot="1">
+    <row r="87" spans="1:7" ht="102.75" thickBot="1">
       <c r="A87" s="5" t="s">
         <v>181</v>
       </c>
@@ -3748,7 +3757,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="88" spans="1:7" ht="88" thickBot="1">
+    <row r="88" spans="1:7" ht="90" thickBot="1">
       <c r="A88" s="2" t="s">
         <v>37</v>
       </c>
@@ -3771,7 +3780,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="89" spans="1:7" ht="75.5" thickBot="1">
+    <row r="89" spans="1:7" ht="77.25" thickBot="1">
       <c r="A89" s="5" t="s">
         <v>38</v>
       </c>
@@ -3794,7 +3803,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="50.5" thickBot="1">
+    <row r="90" spans="1:7" ht="51.75" thickBot="1">
       <c r="A90" s="2" t="s">
         <v>39</v>
       </c>
@@ -3817,7 +3826,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="91" spans="1:7" ht="50.5" thickBot="1">
+    <row r="91" spans="1:7" ht="51.75" thickBot="1">
       <c r="A91" s="5" t="s">
         <v>182</v>
       </c>
@@ -3840,7 +3849,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="63" thickBot="1">
+    <row r="92" spans="1:7" ht="64.5" thickBot="1">
       <c r="A92" s="2" t="s">
         <v>183</v>
       </c>
@@ -3863,7 +3872,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="93" spans="1:7" ht="50">
+    <row r="93" spans="1:7" ht="51.75" thickBot="1">
       <c r="A93" s="6" t="s">
         <v>185</v>
       </c>
@@ -3884,6 +3893,52 @@
       </c>
       <c r="G93" s="6" t="s">
         <v>184</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" ht="64.5" thickBot="1">
+      <c r="A94" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C94" s="4">
+        <v>2024</v>
+      </c>
+      <c r="D94" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E94" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F94" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G94" s="6" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" ht="51">
+      <c r="A95" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C95" s="4">
+        <v>2024</v>
+      </c>
+      <c r="D95" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E95" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F95" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G95" s="6" t="s">
+        <v>82</v>
       </c>
     </row>
   </sheetData>

--- a/data/Tabellarische_Darstellung.xlsx
+++ b/data/Tabellarische_Darstellung.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suma3525\01_TH Wildau\02_Forschung\2024_MK-PM Normen und Standards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E94630A5-A59C-40DF-BE8F-F5F54F022008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A51705-5337-4304-8E6A-12CF1028FDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="59400" yWindow="1605" windowWidth="26925" windowHeight="12825" xr2:uid="{3BF2A3B6-F95D-44C5-B263-B1FCB04FF02A}"/>
+    <workbookView xWindow="5100" yWindow="2355" windowWidth="21600" windowHeight="11175" xr2:uid="{3BF2A3B6-F95D-44C5-B263-B1FCB04FF02A}"/>
   </bookViews>
   <sheets>
     <sheet name="Version 1" sheetId="2" r:id="rId1"/>
@@ -839,28 +839,6 @@
   </si>
   <si>
     <r>
-      <t>A Guide to the Project Management Body of Knowledge PMBOK</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>®</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Guide, 7. Auflage (2021)</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t>Agile: Praxis – Ein Leitfaden (PMI</t>
     </r>
     <r>
@@ -990,6 +968,28 @@
   </si>
   <si>
     <t>Planning Competences ICB4 Reference Guide, Version 1.0 (2024) (added / neu aufgenommen)</t>
+  </si>
+  <si>
+    <r>
+      <t>A Guide to the Project Management Body of Knowledge PMBOK</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>®</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Guide, 8. Auflage (2025) (aktualisiert / updated)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -1856,7 +1856,7 @@
     </row>
     <row r="5" spans="1:7" ht="77.25" thickBot="1">
       <c r="A5" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>109</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="16" spans="1:7" ht="51.75" thickBot="1">
       <c r="A16" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>109</v>
@@ -2132,7 +2132,7 @@
     </row>
     <row r="17" spans="1:7" ht="77.25" thickBot="1">
       <c r="A17" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>108</v>
@@ -2155,7 +2155,7 @@
     </row>
     <row r="18" spans="1:7" ht="102.75" thickBot="1">
       <c r="A18" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>109</v>
@@ -2178,7 +2178,7 @@
     </row>
     <row r="19" spans="1:7" ht="64.5" thickBot="1">
       <c r="A19" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>109</v>
@@ -2201,7 +2201,7 @@
     </row>
     <row r="20" spans="1:7" ht="51.75" thickBot="1">
       <c r="A20" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>109</v>
@@ -2224,7 +2224,7 @@
     </row>
     <row r="21" spans="1:7" ht="64.5" thickBot="1">
       <c r="A21" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>109</v>
@@ -2247,7 +2247,7 @@
     </row>
     <row r="22" spans="1:7" ht="51.75" thickBot="1">
       <c r="A22" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>109</v>
@@ -2270,7 +2270,7 @@
     </row>
     <row r="23" spans="1:7" ht="64.5" thickBot="1">
       <c r="A23" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>109</v>
@@ -2293,7 +2293,7 @@
     </row>
     <row r="24" spans="1:7" ht="77.25" thickBot="1">
       <c r="A24" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>109</v>
@@ -2316,7 +2316,7 @@
     </row>
     <row r="25" spans="1:7" ht="51.75" thickBot="1">
       <c r="A25" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>109</v>
@@ -2339,7 +2339,7 @@
     </row>
     <row r="26" spans="1:7" ht="90" thickBot="1">
       <c r="A26" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>109</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="27" spans="1:7" ht="77.25" thickBot="1">
       <c r="A27" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>109</v>
@@ -2408,7 +2408,7 @@
     </row>
     <row r="29" spans="1:7" ht="64.5" thickBot="1">
       <c r="A29" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>109</v>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="30" spans="1:7" ht="64.5" thickBot="1">
       <c r="A30" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>109</v>
@@ -2454,7 +2454,7 @@
     </row>
     <row r="31" spans="1:7" ht="77.25" thickBot="1">
       <c r="A31" s="5" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>109</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="32" spans="1:7" ht="77.25" thickBot="1">
       <c r="A32" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>109</v>
@@ -2500,7 +2500,7 @@
     </row>
     <row r="33" spans="1:7" ht="90" thickBot="1">
       <c r="A33" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>109</v>
@@ -2523,7 +2523,7 @@
     </row>
     <row r="34" spans="1:7" ht="77.25" thickBot="1">
       <c r="A34" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>109</v>
@@ -2546,7 +2546,7 @@
     </row>
     <row r="35" spans="1:7" ht="90" thickBot="1">
       <c r="A35" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>109</v>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="36" spans="1:7" ht="64.5" thickBot="1">
       <c r="A36" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>109</v>
@@ -2795,7 +2795,7 @@
     </row>
     <row r="46" spans="1:7" ht="77.25" thickBot="1">
       <c r="A46" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>108</v>
@@ -2979,7 +2979,7 @@
     </row>
     <row r="54" spans="1:7" ht="64.5" thickBot="1">
       <c r="A54" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>108</v>
@@ -3002,7 +3002,7 @@
     </row>
     <row r="55" spans="1:7" ht="77.25" thickBot="1">
       <c r="A55" s="5" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>108</v>
@@ -3025,7 +3025,7 @@
     </row>
     <row r="56" spans="1:7" ht="90" thickBot="1">
       <c r="A56" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>108</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="57" spans="1:7" ht="77.25" thickBot="1">
       <c r="A57" s="5" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>108</v>
@@ -3071,7 +3071,7 @@
     </row>
     <row r="58" spans="1:7" ht="77.25" thickBot="1">
       <c r="A58" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>108</v>
@@ -3506,15 +3506,15 @@
         <v>98</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="53.25" thickBot="1">
+    <row r="77" spans="1:7" ht="66" thickBot="1">
       <c r="A77" s="5" t="s">
-        <v>152</v>
+        <v>189</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>108</v>
       </c>
       <c r="C77" s="4">
-        <v>2021</v>
+        <v>2025</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>118</v>
@@ -3713,7 +3713,7 @@
     </row>
     <row r="86" spans="1:7" ht="27.75" thickBot="1">
       <c r="A86" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>108</v>
@@ -3736,7 +3736,7 @@
     </row>
     <row r="87" spans="1:7" ht="102.75" thickBot="1">
       <c r="A87" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>108</v>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="91" spans="1:7" ht="51.75" thickBot="1">
       <c r="A91" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>108</v>
@@ -3851,7 +3851,7 @@
     </row>
     <row r="92" spans="1:7" ht="64.5" thickBot="1">
       <c r="A92" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>108</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="93" spans="1:7" ht="51.75" thickBot="1">
       <c r="A93" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>108</v>
@@ -3883,7 +3883,7 @@
         <v>2020</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="E93" s="6" t="s">
         <v>48</v>
@@ -3892,12 +3892,12 @@
         <v>62</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="64.5" thickBot="1">
       <c r="A94" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>108</v>
@@ -3915,12 +3915,12 @@
         <v>41</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="51">
       <c r="A95" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>108</v>

--- a/data/Tabellarische_Darstellung.xlsx
+++ b/data/Tabellarische_Darstellung.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suma3525\01_TH Wildau\02_Forschung\2024_MK-PM Normen und Standards\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suma3525\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65A51705-5337-4304-8E6A-12CF1028FDDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A93A48-D43A-460F-B879-EADD1B24DECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5100" yWindow="2355" windowWidth="21600" windowHeight="11175" xr2:uid="{3BF2A3B6-F95D-44C5-B263-B1FCB04FF02A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3BF2A3B6-F95D-44C5-B263-B1FCB04FF02A}"/>
   </bookViews>
   <sheets>
     <sheet name="Version 1" sheetId="2" r:id="rId1"/>
@@ -613,28 +613,6 @@
         <rFont val="Arial"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> Project Management Methodology – Guide 3.1 (2021)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>PM</t>
-    </r>
-    <r>
-      <rPr>
-        <vertAlign val="superscript"/>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
       <t xml:space="preserve"> Programme Management Guide 1.0 (2021)</t>
     </r>
   </si>
@@ -989,6 +967,28 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Guide, 8. Auflage (2025) (aktualisiert / updated)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>PM</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Project Management Methodology – Guide 3.1 (2023)</t>
     </r>
   </si>
 </sst>
@@ -1856,7 +1856,7 @@
     </row>
     <row r="5" spans="1:7" ht="77.25" thickBot="1">
       <c r="A5" s="5" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>109</v>
@@ -2109,7 +2109,7 @@
     </row>
     <row r="16" spans="1:7" ht="51.75" thickBot="1">
       <c r="A16" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>109</v>
@@ -2132,7 +2132,7 @@
     </row>
     <row r="17" spans="1:7" ht="77.25" thickBot="1">
       <c r="A17" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B17" s="4" t="s">
         <v>108</v>
@@ -2155,7 +2155,7 @@
     </row>
     <row r="18" spans="1:7" ht="102.75" thickBot="1">
       <c r="A18" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>109</v>
@@ -2178,7 +2178,7 @@
     </row>
     <row r="19" spans="1:7" ht="64.5" thickBot="1">
       <c r="A19" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B19" s="4" t="s">
         <v>109</v>
@@ -2201,7 +2201,7 @@
     </row>
     <row r="20" spans="1:7" ht="51.75" thickBot="1">
       <c r="A20" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>109</v>
@@ -2224,7 +2224,7 @@
     </row>
     <row r="21" spans="1:7" ht="64.5" thickBot="1">
       <c r="A21" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B21" s="4" t="s">
         <v>109</v>
@@ -2247,7 +2247,7 @@
     </row>
     <row r="22" spans="1:7" ht="51.75" thickBot="1">
       <c r="A22" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>109</v>
@@ -2270,7 +2270,7 @@
     </row>
     <row r="23" spans="1:7" ht="64.5" thickBot="1">
       <c r="A23" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B23" s="4" t="s">
         <v>109</v>
@@ -2293,7 +2293,7 @@
     </row>
     <row r="24" spans="1:7" ht="77.25" thickBot="1">
       <c r="A24" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>109</v>
@@ -2316,7 +2316,7 @@
     </row>
     <row r="25" spans="1:7" ht="51.75" thickBot="1">
       <c r="A25" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>109</v>
@@ -2339,7 +2339,7 @@
     </row>
     <row r="26" spans="1:7" ht="90" thickBot="1">
       <c r="A26" s="2" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>109</v>
@@ -2362,7 +2362,7 @@
     </row>
     <row r="27" spans="1:7" ht="77.25" thickBot="1">
       <c r="A27" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B27" s="4" t="s">
         <v>109</v>
@@ -2408,7 +2408,7 @@
     </row>
     <row r="29" spans="1:7" ht="64.5" thickBot="1">
       <c r="A29" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B29" s="4" t="s">
         <v>109</v>
@@ -2431,7 +2431,7 @@
     </row>
     <row r="30" spans="1:7" ht="64.5" thickBot="1">
       <c r="A30" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>109</v>
@@ -2454,7 +2454,7 @@
     </row>
     <row r="31" spans="1:7" ht="77.25" thickBot="1">
       <c r="A31" s="5" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B31" s="4" t="s">
         <v>109</v>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="32" spans="1:7" ht="77.25" thickBot="1">
       <c r="A32" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>109</v>
@@ -2500,7 +2500,7 @@
     </row>
     <row r="33" spans="1:7" ht="90" thickBot="1">
       <c r="A33" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B33" s="4" t="s">
         <v>109</v>
@@ -2523,7 +2523,7 @@
     </row>
     <row r="34" spans="1:7" ht="77.25" thickBot="1">
       <c r="A34" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>109</v>
@@ -2546,7 +2546,7 @@
     </row>
     <row r="35" spans="1:7" ht="90" thickBot="1">
       <c r="A35" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B35" s="4" t="s">
         <v>109</v>
@@ -2569,7 +2569,7 @@
     </row>
     <row r="36" spans="1:7" ht="64.5" thickBot="1">
       <c r="A36" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>109</v>
@@ -2590,13 +2590,13 @@
     </row>
     <row r="37" spans="1:7" ht="40.5" thickBot="1">
       <c r="A37" s="5" t="s">
-        <v>140</v>
+        <v>189</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>108</v>
       </c>
       <c r="C37" s="4">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>122</v>
@@ -2613,7 +2613,7 @@
     </row>
     <row r="38" spans="1:7" ht="40.5" thickBot="1">
       <c r="A38" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>108</v>
@@ -2636,7 +2636,7 @@
     </row>
     <row r="39" spans="1:7" ht="27.75" thickBot="1">
       <c r="A39" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B39" s="4" t="s">
         <v>108</v>
@@ -2728,7 +2728,7 @@
     </row>
     <row r="43" spans="1:7" ht="64.5" thickBot="1">
       <c r="A43" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>108</v>
@@ -2749,7 +2749,7 @@
     </row>
     <row r="44" spans="1:7" ht="39" thickBot="1">
       <c r="A44" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>108</v>
@@ -2795,7 +2795,7 @@
     </row>
     <row r="46" spans="1:7" ht="77.25" thickBot="1">
       <c r="A46" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>108</v>
@@ -2818,7 +2818,7 @@
     </row>
     <row r="47" spans="1:7" ht="53.25" thickBot="1">
       <c r="A47" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>108</v>
@@ -2841,7 +2841,7 @@
     </row>
     <row r="48" spans="1:7" ht="51.75" thickBot="1">
       <c r="A48" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>108</v>
@@ -2864,7 +2864,7 @@
     </row>
     <row r="49" spans="1:7" ht="53.25" thickBot="1">
       <c r="A49" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>108</v>
@@ -2979,7 +2979,7 @@
     </row>
     <row r="54" spans="1:7" ht="64.5" thickBot="1">
       <c r="A54" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>108</v>
@@ -3002,7 +3002,7 @@
     </row>
     <row r="55" spans="1:7" ht="77.25" thickBot="1">
       <c r="A55" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>108</v>
@@ -3025,7 +3025,7 @@
     </row>
     <row r="56" spans="1:7" ht="90" thickBot="1">
       <c r="A56" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>108</v>
@@ -3048,7 +3048,7 @@
     </row>
     <row r="57" spans="1:7" ht="77.25" thickBot="1">
       <c r="A57" s="5" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>108</v>
@@ -3071,7 +3071,7 @@
     </row>
     <row r="58" spans="1:7" ht="77.25" thickBot="1">
       <c r="A58" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>108</v>
@@ -3094,7 +3094,7 @@
     </row>
     <row r="59" spans="1:7" ht="53.25" thickBot="1">
       <c r="A59" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>108</v>
@@ -3140,7 +3140,7 @@
     </row>
     <row r="61" spans="1:7" ht="78.75" thickBot="1">
       <c r="A61" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>108</v>
@@ -3186,7 +3186,7 @@
     </row>
     <row r="63" spans="1:7" ht="40.5" thickBot="1">
       <c r="A63" s="5" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B63" s="4" t="s">
         <v>108</v>
@@ -3209,7 +3209,7 @@
     </row>
     <row r="64" spans="1:7" ht="51.75" thickBot="1">
       <c r="A64" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>108</v>
@@ -3508,7 +3508,7 @@
     </row>
     <row r="77" spans="1:7" ht="66" thickBot="1">
       <c r="A77" s="5" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B77" s="4" t="s">
         <v>108</v>
@@ -3713,7 +3713,7 @@
     </row>
     <row r="86" spans="1:7" ht="27.75" thickBot="1">
       <c r="A86" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>108</v>
@@ -3736,7 +3736,7 @@
     </row>
     <row r="87" spans="1:7" ht="102.75" thickBot="1">
       <c r="A87" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>108</v>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="91" spans="1:7" ht="51.75" thickBot="1">
       <c r="A91" s="5" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="B91" s="4" t="s">
         <v>108</v>
@@ -3851,7 +3851,7 @@
     </row>
     <row r="92" spans="1:7" ht="64.5" thickBot="1">
       <c r="A92" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B92" s="3" t="s">
         <v>108</v>
@@ -3874,7 +3874,7 @@
     </row>
     <row r="93" spans="1:7" ht="51.75" thickBot="1">
       <c r="A93" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B93" s="4" t="s">
         <v>108</v>
@@ -3883,7 +3883,7 @@
         <v>2020</v>
       </c>
       <c r="D93" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="E93" s="6" t="s">
         <v>48</v>
@@ -3892,12 +3892,12 @@
         <v>62</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="94" spans="1:7" ht="64.5" thickBot="1">
       <c r="A94" s="6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B94" s="4" t="s">
         <v>108</v>
@@ -3915,12 +3915,12 @@
         <v>41</v>
       </c>
       <c r="G94" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="95" spans="1:7" ht="51">
       <c r="A95" s="6" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B95" s="4" t="s">
         <v>108</v>

--- a/data/Tabellarische_Darstellung.xlsx
+++ b/data/Tabellarische_Darstellung.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suma3525\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suma3525\01_TH Wildau\02_Forschung\2024_MK-PM Normen und Standards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13A93A48-D43A-460F-B879-EADD1B24DECC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2372439-817B-4F48-B6C9-36D32558AD80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3BF2A3B6-F95D-44C5-B263-B1FCB04FF02A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="188">
   <si>
     <t>ANSI/PMI 08-002-2024, The Standard for Program Management</t>
   </si>
@@ -888,18 +888,6 @@
     <t>DIN ISO 21502:2024-12 Projekt-, Programm- und Portfoliomanagement – Leitlinien zum Projektmanagement (ISO 21502:2020)</t>
   </si>
   <si>
-    <t>DIN ISO 21503:2020-12 Projekt-, Programm- und Portfoliomanagement – Leitlinien zum Programmmanagement (ISO 21503:2017)</t>
-  </si>
-  <si>
-    <t>DIN ISO 21503:2025-03 – Entwurf Projekt-, Programm- und Portfoliomanagement – Leitlinien zum Programmmanagement (ISO 21503:2022)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIN ISO 21504:2017-09 Projekt-, Programm- und Portfoliomanagement – Leitlinien zum Portfoliomanagement (ISO 21504:2015) </t>
-  </si>
-  <si>
-    <t>DIN ISO 21504:2025-04 – Entwurf Projekt-, Programm- und Portfoliomanagement – Leitlinien zum Portfoliomanagement (ISO 21504:2022)</t>
-  </si>
-  <si>
     <t>DIN ISO 21505:2018-01 Projekt-, Programm- und Portfoliomanagement – Leitlinien zu Governance (ISO 21505:2017)</t>
   </si>
   <si>
@@ -990,6 +978,12 @@
       </rPr>
       <t xml:space="preserve"> Project Management Methodology – Guide 3.1 (2023)</t>
     </r>
+  </si>
+  <si>
+    <t>DIN ISO 21503:2025-12 Projekt-, Programm- und Portfoliomanagement – Leitlinien zum Programmmanagement (ISO 21503:2022)  (aktualisiert / updated)</t>
+  </si>
+  <si>
+    <t>DIN ISO 21504:2025-12 Projekt-, Programm- und Portfoliomanagement – Leitlinien zum Portfoliomanagement (ISO 21504:2022) (aktualisiert / updated)</t>
   </si>
 </sst>
 </file>
@@ -1422,8 +1416,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC19F6B0-0587-46B4-B294-E8D476710C92}" name="Tabelle2" displayName="Tabelle2" ref="A1:G95" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
-  <autoFilter ref="A1:G95" xr:uid="{DC19F6B0-0587-46B4-B294-E8D476710C92}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{DC19F6B0-0587-46B4-B294-E8D476710C92}" name="Tabelle2" displayName="Tabelle2" ref="A1:G93" totalsRowShown="0" headerRowDxfId="11" dataDxfId="9" headerRowBorderDxfId="10" tableBorderDxfId="8" totalsRowBorderDxfId="7">
+  <autoFilter ref="A1:G93" xr:uid="{DC19F6B0-0587-46B4-B294-E8D476710C92}"/>
   <tableColumns count="7">
     <tableColumn id="1" xr3:uid="{1EDA15DF-55D2-40A4-885C-A06FCAF5C0D4}" name="Titel" dataDxfId="6"/>
     <tableColumn id="7" xr3:uid="{380A952E-3AB4-42D5-8EA2-4B2FC5008100}" name="Art" dataDxfId="5"/>
@@ -1754,7 +1748,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C876F68F-E5AF-4D2C-A2F8-1E598695C57F}">
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="4" width="21.25" customWidth="1"/>
@@ -1969,7 +1963,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="39" thickBot="1">
+    <row r="10" spans="1:7" ht="40.5" thickBot="1">
       <c r="A10" s="2" t="s">
         <v>136</v>
       </c>
@@ -2475,15 +2469,15 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="77.25" thickBot="1">
+    <row r="32" spans="1:7" ht="90" thickBot="1">
       <c r="A32" s="2" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>109</v>
       </c>
       <c r="C32" s="3">
-        <v>2020</v>
+        <v>2025</v>
       </c>
       <c r="D32" s="3" t="s">
         <v>116</v>
@@ -2499,121 +2493,121 @@
       </c>
     </row>
     <row r="33" spans="1:7" ht="90" thickBot="1">
-      <c r="A33" s="5" t="s">
-        <v>169</v>
-      </c>
-      <c r="B33" s="4" t="s">
+      <c r="A33" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="3">
         <v>2025</v>
       </c>
-      <c r="D33" s="4" t="s">
+      <c r="D33" s="3" t="s">
         <v>116</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F33" s="4" t="s">
         <v>41</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="77.25" thickBot="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="64.5" thickBot="1">
       <c r="A34" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>109</v>
       </c>
       <c r="C34" s="3">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>116</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G34" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" ht="90" thickBot="1">
+        <v>60</v>
+      </c>
+      <c r="G34" s="4"/>
+    </row>
+    <row r="35" spans="1:7" ht="40.5" thickBot="1">
       <c r="A35" s="5" t="s">
-        <v>171</v>
+        <v>185</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C35" s="4">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F35" s="4" t="s">
         <v>41</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="64.5" thickBot="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" ht="40.5" thickBot="1">
       <c r="A36" s="2" t="s">
-        <v>172</v>
+        <v>140</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C36" s="3">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G36" s="4"/>
-    </row>
-    <row r="37" spans="1:7" ht="40.5" thickBot="1">
+        <v>41</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="27.75" thickBot="1">
       <c r="A37" s="5" t="s">
-        <v>189</v>
+        <v>141</v>
       </c>
       <c r="B37" s="4" t="s">
         <v>108</v>
       </c>
       <c r="C37" s="4">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="D37" s="4" t="s">
         <v>122</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F37" s="4" t="s">
         <v>41</v>
       </c>
       <c r="G37" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="40.5" thickBot="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" ht="26.25" thickBot="1">
       <c r="A38" s="2" t="s">
-        <v>140</v>
+        <v>7</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>108</v>
@@ -2625,131 +2619,131 @@
         <v>122</v>
       </c>
       <c r="E38" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G38" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="39" thickBot="1">
+      <c r="A39" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C39" s="4">
+        <v>2021</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="G39" s="4" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="64.5" thickBot="1">
+      <c r="A40" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C40" s="3">
+        <v>2011</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E40" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="F38" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G38" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="27.75" thickBot="1">
-      <c r="A39" s="5" t="s">
-        <v>141</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C39" s="4">
+      <c r="F40" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G40" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="64.5" thickBot="1">
+      <c r="A41" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C41" s="4">
         <v>2022</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G39" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="26.25" thickBot="1">
-      <c r="A40" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C40" s="3">
-        <v>2021</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G40" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="39" thickBot="1">
-      <c r="A41" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C41" s="4">
-        <v>2021</v>
       </c>
       <c r="D41" s="4" t="s">
         <v>123</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G41" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="64.5" thickBot="1">
+        <v>60</v>
+      </c>
+      <c r="G41" s="4"/>
+    </row>
+    <row r="42" spans="1:7" ht="39" thickBot="1">
       <c r="A42" s="2" t="s">
-        <v>9</v>
+        <v>143</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>108</v>
       </c>
       <c r="C42" s="3">
-        <v>2011</v>
+        <v>2019</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>123</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="64.5" thickBot="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="39" thickBot="1">
       <c r="A43" s="5" t="s">
-        <v>142</v>
+        <v>10</v>
       </c>
       <c r="B43" s="4" t="s">
         <v>108</v>
       </c>
       <c r="C43" s="4">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="D43" s="4" t="s">
         <v>123</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G43" s="4"/>
-    </row>
-    <row r="44" spans="1:7" ht="39" thickBot="1">
+        <v>57</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="77.25" thickBot="1">
       <c r="A44" s="2" t="s">
-        <v>143</v>
+        <v>169</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>108</v>
@@ -2758,73 +2752,73 @@
         <v>2019</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>48</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="39" thickBot="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="53.25" thickBot="1">
       <c r="A45" s="5" t="s">
-        <v>10</v>
+        <v>144</v>
       </c>
       <c r="B45" s="4" t="s">
         <v>108</v>
       </c>
       <c r="C45" s="4">
-        <v>2017</v>
+        <v>2025</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>48</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>57</v>
+        <v>41</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="77.25" thickBot="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="51.75" thickBot="1">
       <c r="A46" s="2" t="s">
-        <v>173</v>
+        <v>145</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>108</v>
       </c>
       <c r="C46" s="3">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>48</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="47" spans="1:7" ht="53.25" thickBot="1">
       <c r="A47" s="5" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="B47" s="4" t="s">
         <v>108</v>
       </c>
       <c r="C47" s="4">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>124</v>
@@ -2839,9 +2833,9 @@
         <v>83</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="51.75" thickBot="1">
+    <row r="48" spans="1:7" ht="39" thickBot="1">
       <c r="A48" s="2" t="s">
-        <v>145</v>
+        <v>11</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>108</v>
@@ -2850,21 +2844,21 @@
         <v>2024</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>48</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="G48" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="53.25" thickBot="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="39" thickBot="1">
       <c r="A49" s="5" t="s">
-        <v>146</v>
+        <v>12</v>
       </c>
       <c r="B49" s="4" t="s">
         <v>108</v>
@@ -2873,7 +2867,7 @@
         <v>2024</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>48</v>
@@ -2882,18 +2876,18 @@
         <v>41</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>83</v>
+        <v>61</v>
       </c>
     </row>
     <row r="50" spans="1:7" ht="39" thickBot="1">
       <c r="A50" s="2" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>108</v>
       </c>
       <c r="C50" s="3">
-        <v>2024</v>
+        <v>2020</v>
       </c>
       <c r="D50" s="3" t="s">
         <v>125</v>
@@ -2905,21 +2899,21 @@
         <v>41</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="39" thickBot="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="51.75" thickBot="1">
       <c r="A51" s="5" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B51" s="4" t="s">
         <v>108</v>
       </c>
       <c r="C51" s="4">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>48</v>
@@ -2928,104 +2922,104 @@
         <v>41</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="39" thickBot="1">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="64.5" thickBot="1">
       <c r="A52" s="2" t="s">
-        <v>13</v>
+        <v>170</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>108</v>
       </c>
       <c r="C52" s="3">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>48</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="51.75" thickBot="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="77.25" thickBot="1">
       <c r="A53" s="5" t="s">
-        <v>14</v>
+        <v>171</v>
       </c>
       <c r="B53" s="4" t="s">
         <v>108</v>
       </c>
       <c r="C53" s="4">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>48</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="64.5" thickBot="1">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="90" thickBot="1">
       <c r="A54" s="2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>108</v>
       </c>
       <c r="C54" s="3">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>48</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
     </row>
     <row r="55" spans="1:7" ht="77.25" thickBot="1">
       <c r="A55" s="5" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="B55" s="4" t="s">
         <v>108</v>
       </c>
       <c r="C55" s="4">
-        <v>2025</v>
+        <v>2017</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="90" thickBot="1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="77.25" thickBot="1">
       <c r="A56" s="2" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>108</v>
@@ -3037,116 +3031,116 @@
         <v>119</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F56" s="4" t="s">
         <v>41</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="77.25" thickBot="1">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="53.25" thickBot="1">
       <c r="A57" s="5" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="B57" s="4" t="s">
         <v>108</v>
       </c>
       <c r="C57" s="4">
-        <v>2017</v>
+        <v>2016</v>
       </c>
       <c r="D57" s="4" t="s">
         <v>119</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="77.25" thickBot="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" ht="51.75" thickBot="1">
       <c r="A58" s="2" t="s">
-        <v>178</v>
+        <v>15</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>108</v>
       </c>
       <c r="C58" s="3">
-        <v>2017</v>
+        <v>2023</v>
       </c>
       <c r="D58" s="3" t="s">
         <v>119</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="53.25" thickBot="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="78.75" thickBot="1">
       <c r="A59" s="5" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B59" s="4" t="s">
         <v>108</v>
       </c>
       <c r="C59" s="4">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>119</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="51.75" thickBot="1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="39" thickBot="1">
       <c r="A60" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>108</v>
       </c>
       <c r="C60" s="3">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="D60" s="3" t="s">
         <v>119</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>78</v>
+        <v>41</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="78.75" thickBot="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="40.5" thickBot="1">
       <c r="A61" s="5" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B61" s="4" t="s">
         <v>108</v>
       </c>
       <c r="C61" s="4">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="D61" s="4" t="s">
         <v>119</v>
@@ -3155,70 +3149,70 @@
         <v>48</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>57</v>
+        <v>88</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="39" thickBot="1">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="51.75" thickBot="1">
       <c r="A62" s="2" t="s">
-        <v>16</v>
+        <v>150</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>108</v>
       </c>
       <c r="C62" s="3">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="D62" s="3" t="s">
         <v>119</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="F62" s="4" t="s">
         <v>41</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="40.5" thickBot="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="51.75" thickBot="1">
       <c r="A63" s="5" t="s">
-        <v>149</v>
+        <v>17</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C63" s="4">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>48</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>55</v>
+        <v>75</v>
       </c>
     </row>
     <row r="64" spans="1:7" ht="51.75" thickBot="1">
       <c r="A64" s="2" t="s">
-        <v>150</v>
+        <v>18</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C64" s="3">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>64</v>
@@ -3227,18 +3221,18 @@
         <v>41</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>93</v>
+        <v>76</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="51.75" thickBot="1">
       <c r="A65" s="5" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B65" s="4" t="s">
         <v>109</v>
       </c>
       <c r="C65" s="4">
-        <v>2017</v>
+        <v>2020</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>117</v>
@@ -3250,156 +3244,156 @@
         <v>41</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="51.75" thickBot="1">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="64.5" thickBot="1">
       <c r="A66" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>109</v>
       </c>
       <c r="C66" s="3">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="D66" s="3" t="s">
         <v>117</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
       <c r="F66" s="4" t="s">
         <v>41</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>76</v>
+        <v>40</v>
       </c>
     </row>
     <row r="67" spans="1:7" ht="51.75" thickBot="1">
       <c r="A67" s="5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B67" s="4" t="s">
         <v>109</v>
       </c>
       <c r="C67" s="4">
-        <v>2020</v>
+        <v>2022</v>
       </c>
       <c r="D67" s="4" t="s">
         <v>117</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F67" s="4" t="s">
         <v>41</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="64.5" thickBot="1">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="51.75" thickBot="1">
       <c r="A68" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>109</v>
       </c>
       <c r="C68" s="3">
-        <v>2022</v>
+        <v>2017</v>
       </c>
       <c r="D68" s="3" t="s">
         <v>117</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>41</v>
+        <v>88</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="51.75" thickBot="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="39" thickBot="1">
       <c r="A69" s="5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B69" s="4" t="s">
         <v>109</v>
       </c>
       <c r="C69" s="4">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="D69" s="4" t="s">
         <v>117</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>41</v>
+        <v>72</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
     </row>
     <row r="70" spans="1:7" ht="51.75" thickBot="1">
       <c r="A70" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>109</v>
       </c>
       <c r="C70" s="3">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="D70" s="3" t="s">
         <v>117</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>88</v>
+        <v>41</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="39" thickBot="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="51.75" thickBot="1">
       <c r="A71" s="5" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B71" s="4" t="s">
         <v>109</v>
       </c>
       <c r="C71" s="4">
-        <v>2024</v>
+        <v>2018</v>
       </c>
       <c r="D71" s="4" t="s">
         <v>117</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="51.75" thickBot="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="64.5" thickBot="1">
       <c r="A72" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>109</v>
       </c>
       <c r="C72" s="3">
-        <v>2018</v>
+        <v>2024</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>117</v>
@@ -3408,21 +3402,21 @@
         <v>52</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="G72" s="4" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="51.75" thickBot="1">
+    <row r="73" spans="1:7" ht="64.5" thickBot="1">
       <c r="A73" s="5" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B73" s="4" t="s">
         <v>109</v>
       </c>
       <c r="C73" s="4">
-        <v>2018</v>
+        <v>2025</v>
       </c>
       <c r="D73" s="4" t="s">
         <v>117</v>
@@ -3431,113 +3425,113 @@
         <v>52</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="64.5" thickBot="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="26.25" thickBot="1">
       <c r="A74" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C74" s="3">
-        <v>2024</v>
+        <v>2018</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="64.5" thickBot="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="66" thickBot="1">
       <c r="A75" s="5" t="s">
-        <v>27</v>
+        <v>184</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C75" s="4">
         <v>2025</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="F75" s="4" t="s">
         <v>41</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="26.25" thickBot="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" ht="39" thickBot="1">
       <c r="A76" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B76" s="3" t="s">
         <v>108</v>
       </c>
       <c r="C76" s="3">
+        <v>2025</v>
+      </c>
+      <c r="D76" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E76" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="39" thickBot="1">
+      <c r="A77" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C77" s="4">
         <v>2018</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="E76" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F76" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G76" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="66" thickBot="1">
-      <c r="A77" s="5" t="s">
-        <v>188</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C77" s="4">
-        <v>2025</v>
       </c>
       <c r="D77" s="4" t="s">
         <v>118</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>41</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
     </row>
     <row r="78" spans="1:7" ht="39" thickBot="1">
       <c r="A78" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B78" s="3" t="s">
         <v>108</v>
       </c>
       <c r="C78" s="3">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>118</v>
@@ -3546,44 +3540,44 @@
         <v>48</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="79" spans="1:7" ht="39" thickBot="1">
       <c r="A79" s="5" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B79" s="4" t="s">
         <v>108</v>
       </c>
       <c r="C79" s="4">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="D79" s="4" t="s">
         <v>118</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>73</v>
+        <v>101</v>
       </c>
     </row>
     <row r="80" spans="1:7" ht="39" thickBot="1">
       <c r="A80" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B80" s="3" t="s">
         <v>108</v>
       </c>
       <c r="C80" s="3">
-        <v>2020</v>
+        <v>2019</v>
       </c>
       <c r="D80" s="3" t="s">
         <v>118</v>
@@ -3595,102 +3589,102 @@
         <v>68</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="39" thickBot="1">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="51.75" thickBot="1">
       <c r="A81" s="5" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B81" s="4" t="s">
         <v>108</v>
       </c>
       <c r="C81" s="4">
-        <v>2019</v>
+        <v>2024</v>
       </c>
       <c r="D81" s="4" t="s">
         <v>118</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>68</v>
+        <v>41</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>101</v>
+        <v>53</v>
       </c>
     </row>
     <row r="82" spans="1:7" ht="39" thickBot="1">
       <c r="A82" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B82" s="3" t="s">
         <v>108</v>
       </c>
       <c r="C82" s="3">
-        <v>2019</v>
+        <v>2016</v>
       </c>
       <c r="D82" s="3" t="s">
         <v>118</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" ht="51.75" thickBot="1">
+        <v>60</v>
+      </c>
+      <c r="G82" s="4"/>
+    </row>
+    <row r="83" spans="1:7" ht="26.25" thickBot="1">
       <c r="A83" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B83" s="4" t="s">
         <v>108</v>
       </c>
       <c r="C83" s="4">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>118</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F83" s="4" t="s">
         <v>41</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="39" thickBot="1">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="27.75" thickBot="1">
       <c r="A84" s="2" t="s">
-        <v>35</v>
+        <v>151</v>
       </c>
       <c r="B84" s="3" t="s">
         <v>108</v>
       </c>
       <c r="C84" s="3">
-        <v>2016</v>
+        <v>2018</v>
       </c>
       <c r="D84" s="3" t="s">
         <v>118</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="G84" s="4"/>
-    </row>
-    <row r="85" spans="1:7" ht="26.25" thickBot="1">
+        <v>41</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="102.75" thickBot="1">
       <c r="A85" s="5" t="s">
-        <v>36</v>
+        <v>175</v>
       </c>
       <c r="B85" s="4" t="s">
         <v>108</v>
@@ -3699,7 +3693,7 @@
         <v>2022</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>48</v>
@@ -3708,35 +3702,35 @@
         <v>41</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="27.75" thickBot="1">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="90" thickBot="1">
       <c r="A86" s="2" t="s">
-        <v>151</v>
+        <v>37</v>
       </c>
       <c r="B86" s="3" t="s">
         <v>108</v>
       </c>
       <c r="C86" s="3">
-        <v>2018</v>
+        <v>2022</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>118</v>
+        <v>129</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F86" s="4" t="s">
         <v>41</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="102.75" thickBot="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="77.25" thickBot="1">
       <c r="A87" s="5" t="s">
-        <v>179</v>
+        <v>38</v>
       </c>
       <c r="B87" s="4" t="s">
         <v>108</v>
@@ -3754,125 +3748,125 @@
         <v>41</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="90" thickBot="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="51.75" thickBot="1">
       <c r="A88" s="2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B88" s="3" t="s">
         <v>108</v>
       </c>
       <c r="C88" s="3">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F88" s="4" t="s">
         <v>41</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="77.25" thickBot="1">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="51.75" thickBot="1">
       <c r="A89" s="5" t="s">
-        <v>38</v>
+        <v>176</v>
       </c>
       <c r="B89" s="4" t="s">
         <v>108</v>
       </c>
       <c r="C89" s="4">
-        <v>2022</v>
+        <v>2019</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>48</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>41</v>
+        <v>78</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="51.75" thickBot="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="64.5" thickBot="1">
       <c r="A90" s="2" t="s">
-        <v>39</v>
+        <v>177</v>
       </c>
       <c r="B90" s="3" t="s">
         <v>108</v>
       </c>
       <c r="C90" s="3">
+        <v>2024</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="51.75" thickBot="1">
+      <c r="A91" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C91" s="4">
         <v>2020</v>
       </c>
-      <c r="D90" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="E90" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F90" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G90" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="51.75" thickBot="1">
-      <c r="A91" s="5" t="s">
+      <c r="D91" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B91" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C91" s="4">
-        <v>2019</v>
-      </c>
-      <c r="D91" s="4" t="s">
-        <v>131</v>
-      </c>
-      <c r="E91" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F91" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="G91" s="4" t="s">
-        <v>103</v>
+      <c r="E91" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="64.5" thickBot="1">
-      <c r="A92" s="2" t="s">
+      <c r="A92" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="B92" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C92" s="3">
+      <c r="B92" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="C92" s="4">
         <v>2024</v>
       </c>
-      <c r="D92" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E92" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="F92" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G92" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" ht="51.75" thickBot="1">
+      <c r="D92" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="E92" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="F92" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="G92" s="6" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="51">
       <c r="A93" s="6" t="s">
         <v>183</v>
       </c>
@@ -3880,64 +3874,18 @@
         <v>108</v>
       </c>
       <c r="C93" s="4">
-        <v>2020</v>
-      </c>
-      <c r="D93" s="3" t="s">
-        <v>184</v>
+        <v>2024</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>119</v>
       </c>
       <c r="E93" s="6" t="s">
         <v>48</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>62</v>
+        <v>41</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" ht="64.5" thickBot="1">
-      <c r="A94" s="6" t="s">
-        <v>185</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C94" s="4">
-        <v>2024</v>
-      </c>
-      <c r="D94" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E94" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F94" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G94" s="6" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" ht="51">
-      <c r="A95" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="C95" s="4">
-        <v>2024</v>
-      </c>
-      <c r="D95" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E95" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F95" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="G95" s="6" t="s">
         <v>82</v>
       </c>
     </row>

--- a/data/Tabellarische_Darstellung.xlsx
+++ b/data/Tabellarische_Darstellung.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suma3525\01_TH Wildau\02_Forschung\2024_MK-PM Normen und Standards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2372439-817B-4F48-B6C9-36D32558AD80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A732B23D-7825-4686-810F-11F56989C74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{3BF2A3B6-F95D-44C5-B263-B1FCB04FF02A}"/>
+    <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{3BF2A3B6-F95D-44C5-B263-B1FCB04FF02A}"/>
   </bookViews>
   <sheets>
     <sheet name="Version 1" sheetId="2" r:id="rId1"/>
@@ -111,9 +111,6 @@
     <t>ISO 21506:2024 Project, programme and portfolio management – Vocabulary</t>
   </si>
   <si>
-    <t>ISO 21508:2018  Earned value management in project and programme management</t>
-  </si>
-  <si>
     <t>ISO 21511:2018 Work breakdown structures for project and programme management</t>
   </si>
   <si>
@@ -984,6 +981,10 @@
   </si>
   <si>
     <t>DIN ISO 21504:2025-12 Projekt-, Programm- und Portfoliomanagement – Leitlinien zum Portfoliomanagement (ISO 21504:2022) (aktualisiert / updated)</t>
+  </si>
+  <si>
+    <t>ISO 21508:2026
+Project, programme and portfolio management — Earned value management (aktualisiert/updated)</t>
   </si>
 </sst>
 </file>
@@ -1749,2144 +1750,2144 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C876F68F-E5AF-4D2C-A2F8-1E598695C57F}">
   <dimension ref="A1:G93"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14"/>
   <cols>
     <col min="1" max="4" width="21.25" customWidth="1"/>
-    <col min="5" max="6" width="15.125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="21.125" customWidth="1"/>
+    <col min="5" max="6" width="15.08203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="21.08203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15" thickBot="1">
+    <row r="1" spans="1:7" ht="14.5" thickBot="1">
       <c r="A1" s="1" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>106</v>
-      </c>
       <c r="E1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="77.25" thickBot="1">
+    </row>
+    <row r="2" spans="1:7" ht="75.5" thickBot="1">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C2" s="3">
         <v>2024</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="77.25" thickBot="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="75.5" thickBot="1">
       <c r="A3" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C3" s="4">
         <v>2017</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="77.25" thickBot="1">
+    </row>
+    <row r="4" spans="1:7" ht="75.5" thickBot="1">
       <c r="A4" s="2" t="s">
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C4" s="3">
         <v>2021</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E4" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F4" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="77.25" thickBot="1">
+    </row>
+    <row r="5" spans="1:7" ht="75.5" thickBot="1">
       <c r="A5" s="5" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C5" s="4">
         <v>2019</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="26.25" thickBot="1">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="25.5" thickBot="1">
       <c r="A6" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C6" s="3">
         <v>2025</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="39" thickBot="1">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" ht="38" thickBot="1">
       <c r="A7" s="5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C7" s="4">
         <v>2021</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F7" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G7" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="39" thickBot="1">
+    </row>
+    <row r="8" spans="1:7" ht="38" thickBot="1">
       <c r="A8" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C8" s="3">
         <v>2022</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E8" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F8" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" ht="40.5" thickBot="1">
+    </row>
+    <row r="9" spans="1:7" ht="40" thickBot="1">
       <c r="A9" s="5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" s="4">
         <v>2020</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E9" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" ht="40.5" thickBot="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="40" thickBot="1">
       <c r="A10" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C10" s="3">
         <v>2021</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E10" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F10" s="4" t="s">
+      <c r="G10" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="G10" s="4" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="40.5" thickBot="1">
+    </row>
+    <row r="11" spans="1:7" ht="40" thickBot="1">
       <c r="A11" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C11" s="4">
         <v>2023</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" ht="40.5" thickBot="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" ht="40" thickBot="1">
       <c r="A12" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C12" s="3">
         <v>2018</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" ht="39" thickBot="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="38" thickBot="1">
       <c r="A13" s="5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C13" s="4">
         <v>2021</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" ht="51.75" thickBot="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" ht="50.5" thickBot="1">
       <c r="A14" s="2" t="s">
         <v>4</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C14" s="3">
         <v>2019</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E14" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="39" thickBot="1">
+    </row>
+    <row r="15" spans="1:7" ht="38" thickBot="1">
       <c r="A15" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C15" s="4">
         <v>2020</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F15" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="G15" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="51.75" thickBot="1">
+    </row>
+    <row r="16" spans="1:7" ht="50.5" thickBot="1">
       <c r="A16" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C16" s="3">
         <v>2023</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" ht="77.25" thickBot="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" ht="75.5" thickBot="1">
       <c r="A17" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C17" s="4">
         <v>2019</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F17" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G17" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="G17" s="4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" ht="102.75" thickBot="1">
+    </row>
+    <row r="18" spans="1:7" ht="100.5" thickBot="1">
       <c r="A18" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C18" s="3">
         <v>2014</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" ht="64.5" thickBot="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="63" thickBot="1">
       <c r="A19" s="5" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C19" s="4">
         <v>2009</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" ht="51.75" thickBot="1">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" ht="50.5" thickBot="1">
       <c r="A20" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C20" s="3">
         <v>2009</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E20" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F20" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F20" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="64.5" thickBot="1">
+    </row>
+    <row r="21" spans="1:7" ht="63" thickBot="1">
       <c r="A21" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C21" s="4">
         <v>2009</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" ht="51.75" thickBot="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" ht="50.5" thickBot="1">
       <c r="A22" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C22" s="3">
         <v>2009</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E22" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G22" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F22" s="4" t="s">
-        <v>62</v>
-      </c>
-      <c r="G22" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" ht="64.5" thickBot="1">
+    </row>
+    <row r="23" spans="1:7" ht="63" thickBot="1">
       <c r="A23" s="5" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C23" s="4">
         <v>2009</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F23" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="G23" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" ht="77.25" thickBot="1">
+    </row>
+    <row r="24" spans="1:7" ht="75.5" thickBot="1">
       <c r="A24" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C24" s="3">
         <v>2025</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F24" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="G24" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="G24" s="4" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" ht="51.75" thickBot="1">
+    </row>
+    <row r="25" spans="1:7" ht="50.5" thickBot="1">
       <c r="A25" s="5" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C25" s="4">
         <v>2009</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E25" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G25" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F25" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="G25" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" ht="90" thickBot="1">
+    </row>
+    <row r="26" spans="1:7" ht="88" thickBot="1">
       <c r="A26" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C26" s="3">
         <v>2015</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" ht="77.25" thickBot="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" ht="75.5" thickBot="1">
       <c r="A27" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C27" s="4">
         <v>2015</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" ht="51.75" thickBot="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" ht="50.5" thickBot="1">
       <c r="A28" s="2" t="s">
         <v>6</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C28" s="3">
         <v>2020</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" ht="64.5" thickBot="1">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="75.5" thickBot="1">
       <c r="A29" s="5" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C29" s="4">
         <v>2020</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" ht="64.5" thickBot="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="63" thickBot="1">
       <c r="A30" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C30" s="3">
         <v>2024</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" ht="77.25" thickBot="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" ht="75.5" thickBot="1">
       <c r="A31" s="5" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C31" s="4">
         <v>2024</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E31" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F31" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" ht="90" thickBot="1">
+    </row>
+    <row r="32" spans="1:7" ht="88" thickBot="1">
       <c r="A32" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C32" s="3">
         <v>2025</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" ht="90" thickBot="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" ht="88" thickBot="1">
       <c r="A33" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C33" s="3">
         <v>2025</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F33" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G33" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G33" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" ht="64.5" thickBot="1">
+    </row>
+    <row r="34" spans="1:7" ht="63" thickBot="1">
       <c r="A34" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C34" s="3">
         <v>2018</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G34" s="4"/>
     </row>
-    <row r="35" spans="1:7" ht="40.5" thickBot="1">
+    <row r="35" spans="1:7" ht="40" thickBot="1">
       <c r="A35" s="5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C35" s="4">
         <v>2023</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E35" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F35" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G35" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F35" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G35" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" ht="40.5" thickBot="1">
+    </row>
+    <row r="36" spans="1:7" ht="40" thickBot="1">
       <c r="A36" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C36" s="3">
         <v>2021</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" ht="27.75" thickBot="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" ht="27.5" thickBot="1">
       <c r="A37" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C37" s="4">
         <v>2022</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E37" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F37" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G37" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G37" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" ht="26.25" thickBot="1">
+    </row>
+    <row r="38" spans="1:7" ht="25.5" thickBot="1">
       <c r="A38" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C38" s="3">
         <v>2021</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" ht="39" thickBot="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="38" thickBot="1">
       <c r="A39" s="5" t="s">
         <v>8</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C39" s="4">
         <v>2021</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" ht="64.5" thickBot="1">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" ht="63" thickBot="1">
       <c r="A40" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C40" s="3">
         <v>2011</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F40" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="G40" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="G40" s="4" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" ht="64.5" thickBot="1">
+    </row>
+    <row r="41" spans="1:7" ht="63" thickBot="1">
       <c r="A41" s="5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C41" s="4">
         <v>2022</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G41" s="4"/>
     </row>
-    <row r="42" spans="1:7" ht="39" thickBot="1">
+    <row r="42" spans="1:7" ht="38" thickBot="1">
       <c r="A42" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C42" s="3">
         <v>2019</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" ht="39" thickBot="1">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="38" thickBot="1">
       <c r="A43" s="5" t="s">
         <v>10</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C43" s="4">
         <v>2017</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" ht="77.25" thickBot="1">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" ht="75.5" thickBot="1">
       <c r="A44" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C44" s="3">
         <v>2019</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" ht="53.25" thickBot="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="52.5" thickBot="1">
       <c r="A45" s="5" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C45" s="4">
         <v>2025</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" ht="51.75" thickBot="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="50.5" thickBot="1">
       <c r="A46" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C46" s="3">
         <v>2024</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" ht="53.25" thickBot="1">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" ht="52.5" thickBot="1">
       <c r="A47" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C47" s="4">
         <v>2024</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" ht="39" thickBot="1">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" ht="38" thickBot="1">
       <c r="A48" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C48" s="3">
         <v>2024</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E48" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G48" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F48" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G48" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" ht="39" thickBot="1">
+    </row>
+    <row r="49" spans="1:7" ht="38" thickBot="1">
       <c r="A49" s="5" t="s">
         <v>12</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C49" s="4">
         <v>2024</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="39" thickBot="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" ht="38" thickBot="1">
       <c r="A50" s="2" t="s">
         <v>13</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C50" s="3">
         <v>2020</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" ht="51.75" thickBot="1">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="50.5" thickBot="1">
       <c r="A51" s="5" t="s">
         <v>14</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C51" s="4">
         <v>2023</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" ht="64.5" thickBot="1">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" ht="63" thickBot="1">
       <c r="A52" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C52" s="3">
         <v>2022</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" ht="77.25" thickBot="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" ht="75.5" thickBot="1">
       <c r="A53" s="5" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C53" s="4">
         <v>2025</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" ht="90" thickBot="1">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" ht="88" thickBot="1">
       <c r="A54" s="2" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C54" s="3">
         <v>2017</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" ht="77.25" thickBot="1">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="75.5" thickBot="1">
       <c r="A55" s="5" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C55" s="4">
         <v>2017</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" ht="77.25" thickBot="1">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" ht="75.5" thickBot="1">
       <c r="A56" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C56" s="3">
         <v>2017</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="53.25" thickBot="1">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" ht="52.5" thickBot="1">
       <c r="A57" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C57" s="4">
         <v>2016</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F57" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="G57" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="G57" s="4" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" ht="51.75" thickBot="1">
+    </row>
+    <row r="58" spans="1:7" ht="50.5" thickBot="1">
       <c r="A58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C58" s="3">
         <v>2023</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="78.75" thickBot="1">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="77.5" thickBot="1">
       <c r="A59" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C59" s="4">
         <v>2018</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>91</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="39" thickBot="1">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="38" thickBot="1">
       <c r="A60" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C60" s="3">
         <v>2018</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" ht="40.5" thickBot="1">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" ht="40" thickBot="1">
       <c r="A61" s="5" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C61" s="4">
         <v>2016</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" ht="51.75" thickBot="1">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" ht="50.5" thickBot="1">
       <c r="A62" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C62" s="3">
         <v>2022</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="51.75" thickBot="1">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="50.5" thickBot="1">
       <c r="A63" s="5" t="s">
         <v>17</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C63" s="4">
         <v>2017</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="51.75" thickBot="1">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="50.5" thickBot="1">
       <c r="A64" s="2" t="s">
         <v>18</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C64" s="3">
         <v>2021</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="51.75" thickBot="1">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="50.5" thickBot="1">
       <c r="A65" s="5" t="s">
         <v>19</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C65" s="4">
         <v>2020</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="64.5" thickBot="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="63" thickBot="1">
       <c r="A66" s="2" t="s">
         <v>20</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C66" s="3">
         <v>2022</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="51.75" thickBot="1">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="50.5" thickBot="1">
       <c r="A67" s="5" t="s">
         <v>21</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C67" s="4">
         <v>2022</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="F67" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G67" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="G67" s="4" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="51.75" thickBot="1">
+    </row>
+    <row r="68" spans="1:7" ht="50.5" thickBot="1">
       <c r="A68" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C68" s="3">
         <v>2017</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="39" thickBot="1">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="38" thickBot="1">
       <c r="A69" s="5" t="s">
         <v>23</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C69" s="4">
         <v>2024</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G69" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="63" thickBot="1">
+      <c r="A70" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C70" s="3">
+        <v>2026</v>
+      </c>
+      <c r="D70" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="E70" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F70" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G70" s="4" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="51.75" thickBot="1">
-      <c r="A70" s="2" t="s">
+    <row r="71" spans="1:7" ht="50.5" thickBot="1">
+      <c r="A71" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="B70" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="C70" s="3">
-        <v>2018</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="E70" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F70" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G70" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="51.75" thickBot="1">
-      <c r="A71" s="5" t="s">
-        <v>25</v>
-      </c>
       <c r="B71" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C71" s="4">
         <v>2018</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="64.5" thickBot="1">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="63" thickBot="1">
       <c r="A72" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C72" s="3">
         <v>2024</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="64.5" thickBot="1">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" ht="63" thickBot="1">
       <c r="A73" s="5" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C73" s="4">
         <v>2025</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="26.25" thickBot="1">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" ht="25.5" thickBot="1">
       <c r="A74" s="2" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C74" s="3">
         <v>2018</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="66" thickBot="1">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" ht="65" thickBot="1">
       <c r="A75" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C75" s="4">
         <v>2025</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E75" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G75" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="F75" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="G75" s="4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="39" thickBot="1">
+    </row>
+    <row r="76" spans="1:7" ht="38" thickBot="1">
       <c r="A76" s="2" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C76" s="3">
         <v>2025</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="39" thickBot="1">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" ht="38" thickBot="1">
       <c r="A77" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C77" s="4">
         <v>2018</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="39" thickBot="1">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" ht="38" thickBot="1">
       <c r="A78" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C78" s="3">
         <v>2020</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="39" thickBot="1">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" ht="38" thickBot="1">
       <c r="A79" s="5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C79" s="4">
         <v>2019</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="39" thickBot="1">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" ht="38" thickBot="1">
       <c r="A80" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C80" s="3">
         <v>2019</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" ht="51.75" thickBot="1">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="50.5" thickBot="1">
       <c r="A81" s="5" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C81" s="4">
         <v>2024</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" ht="39" thickBot="1">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="38" thickBot="1">
       <c r="A82" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C82" s="3">
         <v>2016</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G82" s="4"/>
     </row>
-    <row r="83" spans="1:7" ht="26.25" thickBot="1">
+    <row r="83" spans="1:7" ht="25.5" thickBot="1">
       <c r="A83" s="5" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C83" s="4">
         <v>2022</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" ht="27.75" thickBot="1">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" ht="27.5" thickBot="1">
       <c r="A84" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C84" s="3">
         <v>2018</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" ht="102.75" thickBot="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" ht="100.5" thickBot="1">
       <c r="A85" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C85" s="4">
         <v>2022</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" ht="90" thickBot="1">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" ht="88" thickBot="1">
       <c r="A86" s="2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C86" s="3">
         <v>2022</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" ht="77.25" thickBot="1">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" ht="75.5" thickBot="1">
       <c r="A87" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C87" s="4">
         <v>2022</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" ht="51.75" thickBot="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" ht="50.5" thickBot="1">
       <c r="A88" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C88" s="3">
         <v>2020</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" ht="51.75" thickBot="1">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" ht="50.5" thickBot="1">
       <c r="A89" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C89" s="4">
         <v>2019</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" ht="64.5" thickBot="1">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" ht="63" thickBot="1">
       <c r="A90" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C90" s="3">
         <v>2024</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" ht="51.75" thickBot="1">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="50.5" thickBot="1">
       <c r="A91" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C91" s="4">
         <v>2020</v>
       </c>
       <c r="D91" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E91" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="F91" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="G91" s="6" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="63" thickBot="1">
+      <c r="A92" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="E91" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="F91" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="G91" s="6" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" ht="64.5" thickBot="1">
-      <c r="A92" s="6" t="s">
-        <v>181</v>
-      </c>
       <c r="B92" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C92" s="4">
         <v>2024</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E92" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F92" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G92" s="6" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" ht="50">
+      <c r="A93" s="6" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="93" spans="1:7" ht="51">
-      <c r="A93" s="6" t="s">
-        <v>183</v>
-      </c>
       <c r="B93" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C93" s="4">
         <v>2024</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="F93" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G93" s="6" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
   </sheetData>

--- a/data/Tabellarische_Darstellung.xlsx
+++ b/data/Tabellarische_Darstellung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suma3525\01_TH Wildau\02_Forschung\2024_MK-PM Normen und Standards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A732B23D-7825-4686-810F-11F56989C74D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BDE99E7-C2B0-4DE2-A6F1-2AC03FEA1265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{3BF2A3B6-F95D-44C5-B263-B1FCB04FF02A}"/>
   </bookViews>
@@ -983,8 +983,7 @@
     <t>DIN ISO 21504:2025-12 Projekt-, Programm- und Portfoliomanagement – Leitlinien zum Portfoliomanagement (ISO 21504:2022) (aktualisiert / updated)</t>
   </si>
   <si>
-    <t>ISO 21508:2026
-Project, programme and portfolio management — Earned value management (aktualisiert/updated)</t>
+    <t>ISO 21508:2026 Project, programme and portfolio management — Earned value management (aktualisiert/updated)</t>
   </si>
 </sst>
 </file>
@@ -1895,7 +1894,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="38" thickBot="1">
+    <row r="7" spans="1:7" ht="27.5" thickBot="1">
       <c r="A7" s="5" t="s">
         <v>132</v>
       </c>
@@ -1918,7 +1917,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="38" thickBot="1">
+    <row r="8" spans="1:7" ht="27.5" thickBot="1">
       <c r="A8" s="2" t="s">
         <v>133</v>
       </c>
@@ -1964,7 +1963,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="40" thickBot="1">
+    <row r="10" spans="1:7" ht="27.5" thickBot="1">
       <c r="A10" s="2" t="s">
         <v>135</v>
       </c>
@@ -2033,7 +2032,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="38" thickBot="1">
+    <row r="13" spans="1:7" ht="25.5" thickBot="1">
       <c r="A13" s="5" t="s">
         <v>138</v>
       </c>

--- a/data/Tabellarische_Darstellung.xlsx
+++ b/data/Tabellarische_Darstellung.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\suma3525\01_TH Wildau\02_Forschung\2024_MK-PM Normen und Standards\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BDE99E7-C2B0-4DE2-A6F1-2AC03FEA1265}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CB7354D-B783-42D1-810B-293FFCD11AE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-30828" yWindow="-108" windowWidth="30936" windowHeight="16776" xr2:uid="{3BF2A3B6-F95D-44C5-B263-B1FCB04FF02A}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="187">
   <si>
     <t>ANSI/PMI 08-002-2024, The Standard for Program Management</t>
   </si>
@@ -346,9 +346,6 @@
   </si>
   <si>
     <t>Wert, Team</t>
-  </si>
-  <si>
-    <t>Projekmanagement, Prozesse</t>
   </si>
   <si>
     <t>Art</t>
@@ -1758,16 +1755,16 @@
   <sheetData>
     <row r="1" spans="1:7" ht="14.5" thickBot="1">
       <c r="A1" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>105</v>
       </c>
       <c r="E1" s="1" t="s">
         <v>42</v>
@@ -1784,13 +1781,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C2" s="3">
         <v>2024</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E2" s="4" t="s">
         <v>45</v>
@@ -1807,13 +1804,13 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C3" s="4">
         <v>2017</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E3" s="4" t="s">
         <v>46</v>
@@ -1830,13 +1827,13 @@
         <v>2</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C4" s="3">
         <v>2021</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>47</v>
@@ -1850,16 +1847,16 @@
     </row>
     <row r="5" spans="1:7" ht="75.5" thickBot="1">
       <c r="A5" s="5" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C5" s="4">
         <v>2019</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>47</v>
@@ -1876,13 +1873,13 @@
         <v>3</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C6" s="3">
         <v>2025</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>50</v>
@@ -1894,18 +1891,18 @@
         <v>48</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="27.5" thickBot="1">
+    <row r="7" spans="1:7" ht="38" thickBot="1">
       <c r="A7" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C7" s="4">
         <v>2021</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E7" s="4" t="s">
         <v>46</v>
@@ -1917,18 +1914,18 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="27.5" thickBot="1">
+    <row r="8" spans="1:7" ht="38" thickBot="1">
       <c r="A8" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C8" s="3">
         <v>2022</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E8" s="4" t="s">
         <v>51</v>
@@ -1942,16 +1939,16 @@
     </row>
     <row r="9" spans="1:7" ht="40" thickBot="1">
       <c r="A9" s="5" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C9" s="4">
         <v>2020</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E9" s="4" t="s">
         <v>45</v>
@@ -1963,18 +1960,18 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="27.5" thickBot="1">
+    <row r="10" spans="1:7" ht="40" thickBot="1">
       <c r="A10" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C10" s="3">
         <v>2021</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E10" s="4" t="s">
         <v>55</v>
@@ -1988,16 +1985,16 @@
     </row>
     <row r="11" spans="1:7" ht="40" thickBot="1">
       <c r="A11" s="5" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C11" s="4">
         <v>2023</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E11" s="4" t="s">
         <v>47</v>
@@ -2011,16 +2008,16 @@
     </row>
     <row r="12" spans="1:7" ht="40" thickBot="1">
       <c r="A12" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C12" s="3">
         <v>2018</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E12" s="4" t="s">
         <v>47</v>
@@ -2032,18 +2029,18 @@
         <v>54</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="25.5" thickBot="1">
+    <row r="13" spans="1:7" ht="38" thickBot="1">
       <c r="A13" s="5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C13" s="4">
         <v>2021</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E13" s="4" t="s">
         <v>47</v>
@@ -2060,13 +2057,13 @@
         <v>4</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C14" s="3">
         <v>2019</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>47</v>
@@ -2083,13 +2080,13 @@
         <v>5</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C15" s="4">
         <v>2020</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>47</v>
@@ -2103,16 +2100,16 @@
     </row>
     <row r="16" spans="1:7" ht="50.5" thickBot="1">
       <c r="A16" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C16" s="3">
         <v>2023</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>63</v>
@@ -2126,16 +2123,16 @@
     </row>
     <row r="17" spans="1:7" ht="75.5" thickBot="1">
       <c r="A17" s="5" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C17" s="4">
         <v>2019</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E17" s="4" t="s">
         <v>63</v>
@@ -2149,16 +2146,16 @@
     </row>
     <row r="18" spans="1:7" ht="100.5" thickBot="1">
       <c r="A18" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C18" s="3">
         <v>2014</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>47</v>
@@ -2172,16 +2169,16 @@
     </row>
     <row r="19" spans="1:7" ht="63" thickBot="1">
       <c r="A19" s="5" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C19" s="4">
         <v>2009</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>47</v>
@@ -2195,16 +2192,16 @@
     </row>
     <row r="20" spans="1:7" ht="50.5" thickBot="1">
       <c r="A20" s="2" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C20" s="3">
         <v>2009</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>47</v>
@@ -2218,16 +2215,16 @@
     </row>
     <row r="21" spans="1:7" ht="63" thickBot="1">
       <c r="A21" s="5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C21" s="4">
         <v>2009</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E21" s="4" t="s">
         <v>47</v>
@@ -2241,16 +2238,16 @@
     </row>
     <row r="22" spans="1:7" ht="50.5" thickBot="1">
       <c r="A22" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C22" s="3">
         <v>2009</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E22" s="4" t="s">
         <v>47</v>
@@ -2264,16 +2261,16 @@
     </row>
     <row r="23" spans="1:7" ht="63" thickBot="1">
       <c r="A23" s="5" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C23" s="4">
         <v>2009</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>47</v>
@@ -2287,16 +2284,16 @@
     </row>
     <row r="24" spans="1:7" ht="75.5" thickBot="1">
       <c r="A24" s="2" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C24" s="3">
         <v>2025</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>47</v>
@@ -2310,16 +2307,16 @@
     </row>
     <row r="25" spans="1:7" ht="50.5" thickBot="1">
       <c r="A25" s="5" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C25" s="4">
         <v>2009</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>47</v>
@@ -2333,16 +2330,16 @@
     </row>
     <row r="26" spans="1:7" ht="88" thickBot="1">
       <c r="A26" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C26" s="3">
         <v>2015</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>63</v>
@@ -2356,16 +2353,16 @@
     </row>
     <row r="27" spans="1:7" ht="75.5" thickBot="1">
       <c r="A27" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C27" s="4">
         <v>2015</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>63</v>
@@ -2382,13 +2379,13 @@
         <v>6</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C28" s="3">
         <v>2020</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>47</v>
@@ -2402,16 +2399,16 @@
     </row>
     <row r="29" spans="1:7" ht="75.5" thickBot="1">
       <c r="A29" s="5" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C29" s="4">
         <v>2020</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>47</v>
@@ -2425,16 +2422,16 @@
     </row>
     <row r="30" spans="1:7" ht="63" thickBot="1">
       <c r="A30" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C30" s="3">
         <v>2024</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>63</v>
@@ -2448,16 +2445,16 @@
     </row>
     <row r="31" spans="1:7" ht="75.5" thickBot="1">
       <c r="A31" s="5" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C31" s="4">
         <v>2024</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>47</v>
@@ -2471,16 +2468,16 @@
     </row>
     <row r="32" spans="1:7" ht="88" thickBot="1">
       <c r="A32" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C32" s="3">
         <v>2025</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>45</v>
@@ -2494,16 +2491,16 @@
     </row>
     <row r="33" spans="1:7" ht="88" thickBot="1">
       <c r="A33" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C33" s="3">
         <v>2025</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E33" s="4" t="s">
         <v>46</v>
@@ -2517,16 +2514,16 @@
     </row>
     <row r="34" spans="1:7" ht="63" thickBot="1">
       <c r="A34" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C34" s="3">
         <v>2018</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E34" s="4" t="s">
         <v>63</v>
@@ -2538,16 +2535,16 @@
     </row>
     <row r="35" spans="1:7" ht="40" thickBot="1">
       <c r="A35" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C35" s="4">
         <v>2023</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E35" s="4" t="s">
         <v>47</v>
@@ -2561,16 +2558,16 @@
     </row>
     <row r="36" spans="1:7" ht="40" thickBot="1">
       <c r="A36" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C36" s="3">
         <v>2021</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E36" s="4" t="s">
         <v>45</v>
@@ -2584,16 +2581,16 @@
     </row>
     <row r="37" spans="1:7" ht="27.5" thickBot="1">
       <c r="A37" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C37" s="4">
         <v>2022</v>
       </c>
       <c r="D37" s="4" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E37" s="4" t="s">
         <v>46</v>
@@ -2610,13 +2607,13 @@
         <v>7</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C38" s="3">
         <v>2021</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>47</v>
@@ -2633,13 +2630,13 @@
         <v>8</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C39" s="4">
         <v>2021</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E39" s="4" t="s">
         <v>47</v>
@@ -2656,13 +2653,13 @@
         <v>9</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C40" s="3">
         <v>2011</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>45</v>
@@ -2676,16 +2673,16 @@
     </row>
     <row r="41" spans="1:7" ht="63" thickBot="1">
       <c r="A41" s="5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C41" s="4">
         <v>2022</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>51</v>
@@ -2697,16 +2694,16 @@
     </row>
     <row r="42" spans="1:7" ht="38" thickBot="1">
       <c r="A42" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C42" s="3">
         <v>2019</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>47</v>
@@ -2723,13 +2720,13 @@
         <v>10</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C43" s="4">
         <v>2017</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>47</v>
@@ -2743,16 +2740,16 @@
     </row>
     <row r="44" spans="1:7" ht="75.5" thickBot="1">
       <c r="A44" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C44" s="3">
         <v>2019</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>47</v>
@@ -2766,16 +2763,16 @@
     </row>
     <row r="45" spans="1:7" ht="52.5" thickBot="1">
       <c r="A45" s="5" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C45" s="4">
         <v>2025</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>47</v>
@@ -2789,16 +2786,16 @@
     </row>
     <row r="46" spans="1:7" ht="50.5" thickBot="1">
       <c r="A46" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C46" s="3">
         <v>2024</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>47</v>
@@ -2812,16 +2809,16 @@
     </row>
     <row r="47" spans="1:7" ht="52.5" thickBot="1">
       <c r="A47" s="5" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C47" s="4">
         <v>2024</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>47</v>
@@ -2838,13 +2835,13 @@
         <v>11</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C48" s="3">
         <v>2024</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>47</v>
@@ -2861,13 +2858,13 @@
         <v>12</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C49" s="4">
         <v>2024</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>47</v>
@@ -2884,13 +2881,13 @@
         <v>13</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C50" s="3">
         <v>2020</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>47</v>
@@ -2907,13 +2904,13 @@
         <v>14</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C51" s="4">
         <v>2023</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>47</v>
@@ -2927,16 +2924,16 @@
     </row>
     <row r="52" spans="1:7" ht="63" thickBot="1">
       <c r="A52" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C52" s="3">
         <v>2022</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>47</v>
@@ -2950,16 +2947,16 @@
     </row>
     <row r="53" spans="1:7" ht="75.5" thickBot="1">
       <c r="A53" s="5" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C53" s="4">
         <v>2025</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>47</v>
@@ -2973,16 +2970,16 @@
     </row>
     <row r="54" spans="1:7" ht="88" thickBot="1">
       <c r="A54" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C54" s="3">
         <v>2017</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>47</v>
@@ -2996,16 +2993,16 @@
     </row>
     <row r="55" spans="1:7" ht="75.5" thickBot="1">
       <c r="A55" s="5" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C55" s="4">
         <v>2017</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>45</v>
@@ -3019,16 +3016,16 @@
     </row>
     <row r="56" spans="1:7" ht="75.5" thickBot="1">
       <c r="A56" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C56" s="3">
         <v>2017</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>46</v>
@@ -3042,16 +3039,16 @@
     </row>
     <row r="57" spans="1:7" ht="52.5" thickBot="1">
       <c r="A57" s="5" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C57" s="4">
         <v>2016</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>63</v>
@@ -3068,13 +3065,13 @@
         <v>15</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C58" s="3">
         <v>2023</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>63</v>
@@ -3088,16 +3085,16 @@
     </row>
     <row r="59" spans="1:7" ht="77.5" thickBot="1">
       <c r="A59" s="5" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C59" s="4">
         <v>2018</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>47</v>
@@ -3114,13 +3111,13 @@
         <v>16</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C60" s="3">
         <v>2018</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>47</v>
@@ -3134,16 +3131,16 @@
     </row>
     <row r="61" spans="1:7" ht="40" thickBot="1">
       <c r="A61" s="5" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C61" s="4">
         <v>2016</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>47</v>
@@ -3157,16 +3154,16 @@
     </row>
     <row r="62" spans="1:7" ht="50.5" thickBot="1">
       <c r="A62" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C62" s="3">
         <v>2022</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>63</v>
@@ -3183,13 +3180,13 @@
         <v>17</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C63" s="4">
         <v>2017</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>47</v>
@@ -3206,13 +3203,13 @@
         <v>18</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C64" s="3">
         <v>2021</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>63</v>
@@ -3229,13 +3226,13 @@
         <v>19</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C65" s="4">
         <v>2020</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>47</v>
@@ -3252,13 +3249,13 @@
         <v>20</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C66" s="3">
         <v>2022</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>45</v>
@@ -3275,13 +3272,13 @@
         <v>21</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C67" s="4">
         <v>2022</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>46</v>
@@ -3298,13 +3295,13 @@
         <v>22</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C68" s="3">
         <v>2017</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>63</v>
@@ -3321,13 +3318,13 @@
         <v>23</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C69" s="4">
         <v>2024</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>63</v>
@@ -3341,16 +3338,16 @@
     </row>
     <row r="70" spans="1:7" ht="63" thickBot="1">
       <c r="A70" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C70" s="3">
         <v>2026</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>51</v>
@@ -3367,13 +3364,13 @@
         <v>24</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C71" s="4">
         <v>2018</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>51</v>
@@ -3390,13 +3387,13 @@
         <v>25</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C72" s="3">
         <v>2024</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>51</v>
@@ -3413,13 +3410,13 @@
         <v>26</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C73" s="4">
         <v>2025</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>51</v>
@@ -3436,13 +3433,13 @@
         <v>27</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C74" s="3">
         <v>2018</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>51</v>
@@ -3456,16 +3453,16 @@
     </row>
     <row r="75" spans="1:7" ht="65" thickBot="1">
       <c r="A75" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C75" s="4">
         <v>2025</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>47</v>
@@ -3482,13 +3479,13 @@
         <v>28</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C76" s="3">
         <v>2025</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>47</v>
@@ -3505,13 +3502,13 @@
         <v>29</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C77" s="4">
         <v>2018</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>63</v>
@@ -3528,13 +3525,13 @@
         <v>30</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C78" s="3">
         <v>2020</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>47</v>
@@ -3551,13 +3548,13 @@
         <v>31</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C79" s="4">
         <v>2019</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>47</v>
@@ -3574,13 +3571,13 @@
         <v>32</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C80" s="3">
         <v>2019</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>47</v>
@@ -3597,13 +3594,13 @@
         <v>33</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C81" s="4">
         <v>2024</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>63</v>
@@ -3620,13 +3617,13 @@
         <v>34</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C82" s="3">
         <v>2016</v>
       </c>
       <c r="D82" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>63</v>
@@ -3641,13 +3638,13 @@
         <v>35</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C83" s="4">
         <v>2022</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E83" s="4" t="s">
         <v>47</v>
@@ -3661,16 +3658,16 @@
     </row>
     <row r="84" spans="1:7" ht="27.5" thickBot="1">
       <c r="A84" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C84" s="3">
         <v>2018</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E84" s="4" t="s">
         <v>47</v>
@@ -3684,16 +3681,16 @@
     </row>
     <row r="85" spans="1:7" ht="100.5" thickBot="1">
       <c r="A85" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C85" s="4">
         <v>2022</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E85" s="4" t="s">
         <v>47</v>
@@ -3710,13 +3707,13 @@
         <v>36</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C86" s="3">
         <v>2022</v>
       </c>
       <c r="D86" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E86" s="4" t="s">
         <v>45</v>
@@ -3733,13 +3730,13 @@
         <v>37</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C87" s="4">
         <v>2022</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E87" s="4" t="s">
         <v>47</v>
@@ -3756,13 +3753,13 @@
         <v>38</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C88" s="3">
         <v>2020</v>
       </c>
       <c r="D88" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="E88" s="4" t="s">
         <v>47</v>
@@ -3776,16 +3773,16 @@
     </row>
     <row r="89" spans="1:7" ht="50.5" thickBot="1">
       <c r="A89" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C89" s="4">
         <v>2019</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E89" s="4" t="s">
         <v>47</v>
@@ -3799,16 +3796,16 @@
     </row>
     <row r="90" spans="1:7" ht="63" thickBot="1">
       <c r="A90" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C90" s="3">
         <v>2024</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E90" s="4" t="s">
         <v>47</v>
@@ -3817,21 +3814,21 @@
         <v>61</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
     </row>
     <row r="91" spans="1:7" ht="50.5" thickBot="1">
       <c r="A91" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C91" s="4">
         <v>2020</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="E91" s="6" t="s">
         <v>47</v>
@@ -3840,21 +3837,21 @@
         <v>61</v>
       </c>
       <c r="G91" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="92" spans="1:7" ht="63" thickBot="1">
       <c r="A92" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C92" s="4">
         <v>2024</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>47</v>
@@ -3863,21 +3860,21 @@
         <v>40</v>
       </c>
       <c r="G92" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="93" spans="1:7" ht="50">
       <c r="A93" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C93" s="4">
         <v>2024</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E93" s="6" t="s">
         <v>47</v>
